--- a/backend/STRESS_TEST_REPORT_200.xlsx
+++ b/backend/STRESS_TEST_REPORT_200.xlsx
@@ -93,9 +93,128 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2667000" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2667000" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2667000" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -144,7 +263,11 @@
           <t>社区团购选品小程序</t>
         </is>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>社区团购选品小程序需要传达亲切、可信和高频浏览的感觉；采用清爽的自然系底色和轻量卡片能突出商品信息与价格比较，同时圆角与柔和绿色强化“社区、健康、实惠”的视觉联想。</t>
+        </is>
+      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>SUCCESS</t>
@@ -153,16 +276,73 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>/Users/eric/workspace/lingnow/backend/target/stress-html/verify-0.html</t>
+          <t>/Users/eric/workspace/lingnow/backend/target/stress-html/verify-v4-0.html</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>{"visual_bgClass":"bg-emerald-50","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"完成社区商品选品并上架\",\"steps\":[\"首页 -&gt; 进入选品池 -&gt; 筛选高毛利商品 -&gt; 打开商品详情 -&gt; 加入选品车 -&gt; 团长工作台上架 -&gt; 分享到社群\"]},{\"id\":\"flow_2\",\"description\":\"对比多个候选商品并确定最终上架品\",\"steps\":[\"选品池 -&gt; 选择多个商品 -&gt; 进入对比面板 -&gt; 查看销量、利润、缺货率 -&gt; 确认最优商品 -&gt; 保存为推荐方案\"]},{\"id\":\"flow_3\",\"description\":\"查看订单履约与异常处理\",\"steps\":[\"团长工作台 -&gt; 查看预售进度 -&gt; 进入订单跟踪 -&gt; 识别缺货或延迟 -&gt; 发起售后处理 -&gt; 完成异常关闭\"]},{\"id\":\"flow_4\",\"description\":\"复盘选品效果并优化下次推荐\",\"steps\":[\"经营分析 -&gt; 查看本周表现 -&gt; 对比各商品转化与利润 -&gt; 定位低效品类 -&gt; 调整选品规则 -&gt; 生成下次推荐策略\"]}]","visual_primaryColor":"emerald-600","visual_fontFamily":"font-sans","visual_cardClass":"bg-white border border-emerald-100 shadow-sm rounded-2xl","visual_reasoning":"社区团购选品小程序需要传达亲切、可信和高频浏览的感觉；采用清爽的自然系底色和轻量卡片能突出商品信息与价格比较，同时圆角与柔和绿色强化“社区、健康、实惠”的视觉联想。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-emerald-600 text-white shadow-sm hover:bg-emerald-700","functional_audit_result":"CORRECTION_NEEDED:  \n1. **Flow 1 broken in page-level traversal**\n   - `经营总览` should link to `商品池管理`, and `商品池管理` should lead to `筛选高潜商品 -&gt; 创建拼团活动 -&gt; 上架成功`.\n   - Although there are links to `#pg3` and `#pg1-flow1`, the actual target pages for the flow are inconsistent: `#pg3` is the product pool page, but the flow text on `#pg1-flow1` only provides a link to `#pg1-pool` and `#pg1-analysis`, not a complete traversal to a real `上架成功` page/state.\n   - `创建拼团活动` exists as a button/link, but there is **no actual success page or success state** for `上架成功`.\n\n2. **Flow 2 broken by page-hash mismatch**\n   - Required: `经营总览 -&gt; 订单与履约管理 -&gt; 查看异常订单 -&gt; 处理缺货或延迟 -&gt; 订单状态更新成功`\n   - The prototype’s `经营总览` page uses `#pg1-orders`, but the dedicated `订单与履约管理` traversal is inconsistently split across `#pg4` and `#pg5`.\n   - In `#pg4`, the step 1 link for `订单与履约管理` incorrectly points to `#pg3`, not the actual orders page.\n   - The `查看异常订单` / `处理缺货或延迟` / `订单状态更新成功` steps are present as labels, but there is **no complete linked sequence** and no real success state page for status update.\n\n3. **Flow 3 broken by incorrect navigation target**\n   - Required: `经营总览 -&gt; 经营分析 -&gt; 查看活动数据 -&gt; 对比商品表现 -&gt; 生成选品优化建议`\n   - `经营总览` does link to `#pg1-analysis`, but the analysis pages are fragmented between `#pg1-analysis`, `#pg2`, `#pg5`, and `#pg6`.\n   - The `查看活动数据` step is not consistently linked from the analysis entry point to a concrete detailed page.\n   - The UI shows “生成选品优化建议” text/buttons, but there is **no end-to-end traversable action path** from activity data to comparison to suggestion generation on a single logical route.\n\n4. **Flow 4 broken by missing actual save state**\n   - Required: `经营总览 -&gt; 商品池管理 -&gt; 查看社区偏好标签 -&gt; 推荐商品入池 -&gt; 保存成功`\n   - There are links for `经营总览`, `商品池管理`, and `查看社区偏好标签`.\n   - However, `推荐商品入池` only navigates around the product pool and there is **no actual save confirmation page/state** for `保存成功`.\n   - The prototype includes a button labeled `保存成功`, but it is not connected as a meaningful submission result or success screen.\n\n5. **General issue: inconsistent hash/page structure**\n   - Several task flow labels point to hash anchors that do not correspond cleanly to the required journey order.\n   - Some flows are represented as text blocks/buttons only, without a real linked destination or success state.\n   - Core action completion states (`上架成功`, `订单状态更新成功`, `生成选品优化建议`, `保存成功`) are missing as traversable results."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customHeight="true" ht="100.0">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>深夜食堂在线预约单</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>深夜食堂在线预约单适合夜间氛围：用深色背景营造深夜、温暖、安静的用餐感受；琥珀色作为主色传达灯光与食欲；卡片与按钮保持中等圆角，兼顾亲切感和效率，适合预约这种高频、信息密度中等的服务场景。</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>/Users/eric/workspace/lingnow/backend/target/stress-html/verify-v4-1.html</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>{"visual_bgClass":"bg-stone-950","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"完成深夜食堂预约单\",\"steps\":[\"进入 /预约总览 -&gt; 选择可订门店 -&gt; 跳转 /新建预约 -&gt; 填写人数、时间、偏好 -&gt; 提交预约 -&gt; 成功提示与通知发送\"]},{\"id\":\"flow_2\",\"description\":\"门店确认并核销预约\",\"steps\":[\"进入 /预约详情 -&gt; 检查联系人与备注 -&gt; 前往 /到店核销 -&gt; 输入核销码 -&gt; 确认到店 -&gt; 更新状态为已履约\"]},{\"id\":\"flow_3\",\"description\":\"运营侧优化夜间时段\",\"steps\":[\"进入 /时段运营 -&gt; 查看热力图与取消趋势 -&gt; 调整容量与营业策略 -&gt; 发布时段变更 -&gt; 用户端收到消息通知\"]}]","visual_primaryColor":"amber-500","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/90 border border-stone-700 shadow-2xl","visual_reasoning":"深夜食堂在线预约单适合夜间氛围：用深色背景营造深夜、温暖、安静的用餐感受；琥珀色作为主色传达灯光与食欲；卡片与按钮保持中等圆角，兼顾亲切感和效率，适合预约这种高频、信息密度中等的服务场景。","lang":"ZH","visual_buttonClass":"rounded-xl bg-amber-500 text-stone-950 font-semibold shadow-lg hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED: [\n  \"flow_1（完成深夜预约）: 步骤要求为“预约总览 -&gt; 在线预约单 -&gt; 填写人数与时间 -&gt; 提交预约 -&gt; 预约成功页”，但页面之间没有真实可达的 #hash 流转链路。虽然存在 #flow_1 / #pg3-submit / #pg3-success / #pg4-success 等锚点文字，但缺少明确从“预约总览”进入“在线预约单”的可执行链接，以及“填写人数与时间”对应的独立页面/步骤页。\",\n  \"flow_1: 预约成功页缺失。代码中多处链接指向 #pg3-success、#pg4-success，但 HTML 中没有对应的 #pg3-success 或 #pg4-success 页面内容。\",\n  \"flow_2（提前预点夜宵）: 步骤要求为“预约总览 -&gt; 菜单与加购 -&gt; 选择菜品 -&gt; 确认加购 -&gt; 预约确认页”，但“选择菜品”与“确认加购”没有独立的可遍历页面/步骤页，主要只是列表按钮；且“预约确认页”虽在部分位置写有文案，但缺少稳定对应的唯一页面锚点闭环。\",\n  \"flow_2: 多处“菜单与加购/确认加购”按钮仅指向同一页面内的 flow 锚点或当前页，缺少从“选择菜品”到“确认加购”再到“预约确认页”的清晰逐步跳转链路。\",\n  \"flow_3（门店处理高峰预约）: 步骤要求为“门店运营 -&gt; 查看预约队列 -&gt; 自动分配座位 -&gt; 扫码核销 -&gt; 到店成功提示”，但“自动分配座位”“扫码核销”“到店成功提示”没有形成明确、连续的页面跳转链路；大量按钮仅指向 #flow_3 或同页标签，缺少独立步骤页。\",\n  \"flow_3: 页面中存在 #pg3-checkin / #pg4-checkin / #pg3-verify 等引用，但没有完整且一致的“到店成功提示”落地页面锚点。\",\n  \"flow_4（处理迟到与释放座位）: 步骤要求为“门店运营 -&gt; 识别超时未到 -&gt; 标记迟到 -&gt; 释放座位 -&gt; 通知候补顾客”，但页面仅有“迟到与取消提醒/释放座位”相关文案与按钮，缺少“识别超时未到”“标记迟到”“通知候补顾客”的独立可遍历页面或明确跳转路径。\",\n  \"flow_4: 存在多个迟到/释放座位入口，但没有从门店运营页到该流程每一步的明确 #hash 链路，导致任务流不可完整验证。\",\n  \"全局问题: 该原型包含多个重复/并列页面段（#pg1, #pg2, #pg3, #pg4, #pg5, #pg6），但任务流要求的关键节点（如填写人数与时间、选择菜品、自动分配座位、扫码核销、到店成功提示、标记迟到、通知候补顾客）大多没有对应的独立步骤页或一致的锚点命名，导致核心任务流不可严格按步骤遍历。\"\n]"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" customHeight="true" ht="100.0">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>精酿啤酒口味评分系统</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>精酿啤酒评分系统适合偏夜店/酒吧式的深色氛围，能突出品鉴、醇厚、专业感；琥珀色作为主色联想到酒液与麦芽，配合较高密度布局，便于快速记录风味维度与评分。</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>/Users/eric/workspace/lingnow/backend/target/stress-html/verify-v4-2.html</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>{"visual_bgClass":"bg-stone-950","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"完成一次精酿啤酒评分\",\"steps\":[\"评分工作台 -&gt; 选择酒款 -&gt; 填写香气/苦度/酒体等评分 -&gt; 选择风味标签 -&gt; 保存评分 -&gt; 生成评分结果页\"]},{\"id\":\"flow_2\",\"description\":\"通过个人口味画像发现新酒款\",\"steps\":[\"风味画像 -&gt; 查看偏好总结 -&gt; 进入推荐发现 -&gt; 浏览推荐酒款 -&gt; 打开酒款详情 -&gt; 收藏或加入品鉴清单\"]},{\"id\":\"flow_3\",\"description\":\"对比多款精酿啤酒并做决策\",\"steps\":[\"酒款库 -&gt; 选择多款酒 -&gt; 进入对比页 -&gt; 查看风味差异与评分维度 -&gt; 输出对比结论 -&gt; 收藏优胜酒款\"]},{\"id\":\"flow_4\",\"description\":\"商家查看市场偏好分析\",\"steps\":[\"数据分析 -&gt; 选择时间范围与区域 -&gt; 查看评分趋势 -&gt; 分析风味偏好变化 -&gt; 导出报表 -&gt; 制定选品策略\"]}]","visual_primaryColor":"amber-500","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/80 border border-stone-700 shadow-xl shadow-black/20 backdrop-blur","visual_reasoning":"精酿啤酒评分系统适合偏夜店/酒吧式的深色氛围，能突出品鉴、醇厚、专业感；琥珀色作为主色联想到酒液与麦芽，配合较高密度布局，便于快速记录风味维度与评分。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-amber-500 text-stone-950 font-semibold hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED: [\n  \"flow_1: 虽然存在“口味总览 -&gt; 快速评分”链接，以及“提交评分 / 生成风味图谱”按钮，但“填写多维度评分与风味标签”这一关键步骤在交互上没有真正可填写的表单控件，只有静态展示/按钮，缺少明确的输入与提交动作闭环。\",\n  \"flow_1: “提交成功并生成风味图谱”在多个页面中只是跳转到锚点页面或预览区，没有明确从快速评分页直接到“提交成功/风味图谱”的可靠 hash 路径闭环；部分按钮指向的锚点页并不对应实际独立成功页。\",\n  \"flow_2: “口味总览 -&gt; 个人口味画像 -&gt; 个性推荐列表 -&gt; 查看酒款详情 -&gt; 加入收藏”路径不完整。虽然页面中有“个人口味画像”“个性推荐列表”“查看详情”“加入收藏”按钮，但多个按钮都仍指向同一 flow/页面锚点，而不是明确从总览页逐层跳转到对应详情页。\",\n  \"flow_2: “查看酒款详情”缺少明确可达的独立详情内容页面映射；部分链接仅指向 #pg2-detail、#beer-detail 等，但在主流程中并未形成从推荐列表到详情再到收藏的稳定、唯一可追踪路径。\",\n  \"flow_3: “风味图谱 -&gt; 选择风格筛选 -&gt; 多酒款横向对比 -&gt; 查看差异洞察 -&gt; 保存对比结果”存在部分缺口：虽然有“同风格对比/保存对比结果/查看差异洞察”按钮，但缺少真正的“风格筛选”交互控件，只有静态文案和卡片展示，没有可操作的筛选器。\",\n  \"flow_3: “多酒款横向对比”与“查看差异洞察”虽有相关内容区，但部分链接指向的锚点（如 #pg2-detail、#compare-detail）并未提供完整、清晰的对比结果落点，保存结果也多为跳转式占位。\",\n  \"flow_4: “商家洞察 -&gt; 查看评分总览与趋势 -&gt; 定位差评集中点 -&gt; 调整菜单与上新策略 -&gt; 复看优化效果”虽在页面中出现对应模块，但路径分散在多个不同 hash 版本（#pg2、#pg3、#pg4、#pg5、#pg6），没有一个稳定的单一路径可从商家洞察页连续走完。\",\n  \"flow_4: “调整菜单与上新策略”没有明确的提交/保存动作按钮，只看到建议列表与“菜单优化”展示，缺少执行优化策略的核心 action。\",\n  \"整体: 该原型包含大量重复且分散的页面版本，很多任务流依赖的页面锚点并非从当前页面逐步可达，存在明显的锚点碎片化与路径不唯一问题，导致任务流无法被严格验证为逻辑可遍历。\"\n]"}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/STRESS_TEST_REPORT_200.xlsx
+++ b/backend/STRESS_TEST_REPORT_200.xlsx
@@ -265,7 +265,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>社区团购选品小程序需要传达亲切、可信和高频浏览的感觉；采用清爽的自然系底色和轻量卡片能突出商品信息与价格比较，同时圆角与柔和绿色强化“社区、健康、实惠”的视觉联想。</t>
+          <t>社区团购选品小程序的核心心理是“可信、清晰、效率优先”。它不是强情绪消费型产品，而是围绕团长、供应链和社区成员的高频决策工具，因此视觉上需要建立稳定、专业、低噪音的信任感。整体采用偏 slate/indigo 的深色中性色系，能传达供应链管理、数据判断和价格秩序感；卡片以 Solid Paper 为主，配合明确边界与适度阴影，强调信息分层和可扫读性，适合商品列表、规格对比、销量与库存状态等高密度内容。适度的玻璃模糊只作为辅助层，用于营造现代感和轻量层级，而不是喧宾夺主。翠绿作为点缀，天然对应“选品、上架、热卖、增长”这类正向操作反馈，同时也能强化生鲜、社区生活类商品的亲和力。整体气质应是“高效率的社区供给中枢”：既要让团长快速做出判断，也要让用户感到货源靠谱、价格透明、选择有序。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -281,7 +281,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-emerald-50","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"完成社区商品选品并上架\",\"steps\":[\"首页 -&gt; 进入选品池 -&gt; 筛选高毛利商品 -&gt; 打开商品详情 -&gt; 加入选品车 -&gt; 团长工作台上架 -&gt; 分享到社群\"]},{\"id\":\"flow_2\",\"description\":\"对比多个候选商品并确定最终上架品\",\"steps\":[\"选品池 -&gt; 选择多个商品 -&gt; 进入对比面板 -&gt; 查看销量、利润、缺货率 -&gt; 确认最优商品 -&gt; 保存为推荐方案\"]},{\"id\":\"flow_3\",\"description\":\"查看订单履约与异常处理\",\"steps\":[\"团长工作台 -&gt; 查看预售进度 -&gt; 进入订单跟踪 -&gt; 识别缺货或延迟 -&gt; 发起售后处理 -&gt; 完成异常关闭\"]},{\"id\":\"flow_4\",\"description\":\"复盘选品效果并优化下次推荐\",\"steps\":[\"经营分析 -&gt; 查看本周表现 -&gt; 对比各商品转化与利润 -&gt; 定位低效品类 -&gt; 调整选品规则 -&gt; 生成下次推荐策略\"]}]","visual_primaryColor":"emerald-600","visual_fontFamily":"font-sans","visual_cardClass":"bg-white border border-emerald-100 shadow-sm rounded-2xl","visual_reasoning":"社区团购选品小程序需要传达亲切、可信和高频浏览的感觉；采用清爽的自然系底色和轻量卡片能突出商品信息与价格比较，同时圆角与柔和绿色强化“社区、健康、实惠”的视觉联想。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-emerald-600 text-white shadow-sm hover:bg-emerald-700","functional_audit_result":"CORRECTION_NEEDED:  \n1. **Flow 1 broken in page-level traversal**\n   - `经营总览` should link to `商品池管理`, and `商品池管理` should lead to `筛选高潜商品 -&gt; 创建拼团活动 -&gt; 上架成功`.\n   - Although there are links to `#pg3` and `#pg1-flow1`, the actual target pages for the flow are inconsistent: `#pg3` is the product pool page, but the flow text on `#pg1-flow1` only provides a link to `#pg1-pool` and `#pg1-analysis`, not a complete traversal to a real `上架成功` page/state.\n   - `创建拼团活动` exists as a button/link, but there is **no actual success page or success state** for `上架成功`.\n\n2. **Flow 2 broken by page-hash mismatch**\n   - Required: `经营总览 -&gt; 订单与履约管理 -&gt; 查看异常订单 -&gt; 处理缺货或延迟 -&gt; 订单状态更新成功`\n   - The prototype’s `经营总览` page uses `#pg1-orders`, but the dedicated `订单与履约管理` traversal is inconsistently split across `#pg4` and `#pg5`.\n   - In `#pg4`, the step 1 link for `订单与履约管理` incorrectly points to `#pg3`, not the actual orders page.\n   - The `查看异常订单` / `处理缺货或延迟` / `订单状态更新成功` steps are present as labels, but there is **no complete linked sequence** and no real success state page for status update.\n\n3. **Flow 3 broken by incorrect navigation target**\n   - Required: `经营总览 -&gt; 经营分析 -&gt; 查看活动数据 -&gt; 对比商品表现 -&gt; 生成选品优化建议`\n   - `经营总览` does link to `#pg1-analysis`, but the analysis pages are fragmented between `#pg1-analysis`, `#pg2`, `#pg5`, and `#pg6`.\n   - The `查看活动数据` step is not consistently linked from the analysis entry point to a concrete detailed page.\n   - The UI shows “生成选品优化建议” text/buttons, but there is **no end-to-end traversable action path** from activity data to comparison to suggestion generation on a single logical route.\n\n4. **Flow 4 broken by missing actual save state**\n   - Required: `经营总览 -&gt; 商品池管理 -&gt; 查看社区偏好标签 -&gt; 推荐商品入池 -&gt; 保存成功`\n   - There are links for `经营总览`, `商品池管理`, and `查看社区偏好标签`.\n   - However, `推荐商品入池` only navigates around the product pool and there is **no actual save confirmation page/state** for `保存成功`.\n   - The prototype includes a button labeled `保存成功`, but it is not connected as a meaningful submission result or success screen.\n\n5. **General issue: inconsistent hash/page structure**\n   - Several task flow labels point to hash anchors that do not correspond cleanly to the required journey order.\n   - Some flows are represented as text blocks/buttons only, without a real linked destination or success state.\n   - Core action completion states (`上架成功`, `订单状态更新成功`, `生成选品优化建议`, `保存成功`) are missing as traversable results."}</t>
+          <t>{"visual_bgClass":"bg-slate-950/95","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"爆品选品并发起团购\",\"steps\":[\"进入爆品推荐中心 -&gt; 查看社区热销榜 -&gt; 选择高毛利商品 -&gt; 加入选品清单 -&gt; 跳转团购活动配置 -&gt; 发布活动成功\"]},{\"id\":\"flow_2\",\"description\":\"批量筛选商品并完成上架\",\"steps\":[\"进入选品清单管理 -&gt; 设置价格带与品类筛选 -&gt; 对比商品销量与库存 -&gt; 批量加入清单 -&gt; 生成活动商品列表 -&gt; 上架完成\"]},{\"id\":\"flow_3\",\"description\":\"处理库存预警并替换商品\",\"steps\":[\"进入库存与履约监控 -&gt; 查看缺货预警列表 -&gt; 识别风险商品 -&gt; 返回选品清单管理 -&gt; 替换为可售商品 -&gt; 重新保存活动\"]},{\"id\":\"flow_4\",\"description\":\"活动结束后复盘优化\",\"steps\":[\"进入数据复盘分析 -&gt; 查看销量趋势与毛利分析 -&gt; 定位高转化商品 -&gt; 标记低效商品 -&gt; 生成下一轮选品建议\"]}]","visual_primaryColor":"indigo-500","visual_fontFamily":"font-sans","visual_cardClass":"bg-slate-900/80 border border-slate-800/60 rounded-2xl shadow-xl","visual_reasoning":"社区团购选品小程序的核心心理是“可信、清晰、效率优先”。它不是强情绪消费型产品，而是围绕团长、供应链和社区成员的高频决策工具，因此视觉上需要建立稳定、专业、低噪音的信任感。整体采用偏 slate/indigo 的深色中性色系，能传达供应链管理、数据判断和价格秩序感；卡片以 Solid Paper 为主，配合明确边界与适度阴影，强调信息分层和可扫读性，适合商品列表、规格对比、销量与库存状态等高密度内容。适度的玻璃模糊只作为辅助层，用于营造现代感和轻量层级，而不是喧宾夺主。翠绿作为点缀，天然对应“选品、上架、热卖、增长”这类正向操作反馈，同时也能强化生鲜、社区生活类商品的亲和力。整体气质应是“高效率的社区供给中枢”：既要让团长快速做出判断，也要让用户感到货源靠谱、价格透明、选择有序。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-emerald-600 text-white shadow-sm hover:bg-emerald-700","functional_audit_result":"CORRECTION_NEEDED: \n1. flow_1 / flow_2 / flow_3 / flow_4 all reference navigation into pages that are not actually traversable via matching hash links from the intended source pages:\n   - The sidebar links go to #pg1–#pg13, but the task flows require transitions like “进入选品中心 -&gt; 使用多维筛选条件 -&gt; 打开商品详情 -&gt; 加入选品清单 -&gt; 一键上架到团购池”.\n   - In several places the prototype uses placeholder hashes such as #drawer-open, #list-add, #group-buy-pool, #analytics-risk that do not correspond to real routed pages/sections with those IDs.\n\n2. flow_1 broken path:\n   - “打开商品详情” from 选品中心 exists only as click-to-open drawer behavior, but there is no hash link from 选品中心 to 商品详情 page/section as required by the audit rule.\n   - “加入选品清单” and “一键上架到团购池” appear as anchors, but many point to placeholder hashes or same-page placeholders rather than a concrete traversable route.\n   - The intended completion flow is not explicitly connected end-to-end with a stable hash path.\n\n3. flow_2 broken path:\n   - “查看智能推荐理由” is present on pg4, but the route to a distinct page/section for recommendation details is incomplete/inconsistent.\n   - “标记通过” / “淘汰” buttons exist in drawers, but they point to #drawer-open or same current hash instead of a dedicated actionable destination, so the evaluation flow is not logically traversable per hash-link rule.\n\n4. flow_3 broken path:\n   - “进入数据看板” exists, but “查看补货预警与滞销列表” and “打开商品详情” are not connected through a clear hash-based page sequence.\n   - “调整活动或补货建议” is shown as information, but there is no actionable button/link to a dedicated adjustment page or anchored workflow.\n   - “更新选品清单” exists, but again is not part of a fully linked end-to-end route.\n\n5. flow_4 broken path:\n   - “进入数据看板 -&gt; 选择品类或时间范围 -&gt; 查看供应商中心与商品表现 -&gt; 标记高风险供应商 -&gt; 优化后续选品策略” is only partially represented.\n   - There is no distinct, hash-addressable control for “标记高风险供应商”; current UI only displays supplier risk cards and generic strategy text.\n   - The “优化后续选品策略” action is informational, not a traversable action button tied to a destination.\n\n6. Data consistency issues:\n   - Several links reference pages/targets not defined by IDs in the DOM, causing the prototype to fail the hash-based traversal requirement.\n   - Some actions are duplicated as non-functional buttons in the global drawer and page content without a clear submit/complete step.\n\n","visual_accentColor":"emerald-400","visual_shadowStrategy":"shadow-xl","visual_borderAccent":"border-slate-800/50","visual_glassIntensity":"backdrop-blur-md"}</t>
         </is>
       </c>
     </row>
@@ -293,7 +293,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>深夜食堂在线预约单适合夜间氛围：用深色背景营造深夜、温暖、安静的用餐感受；琥珀色作为主色传达灯光与食欲；卡片与按钮保持中等圆角，兼顾亲切感和效率，适合预约这种高频、信息密度中等的服务场景。</t>
+          <t>深夜食堂在线预约单的核心心理不是“冷酷科技”，而是“夜间安心感 + 食欲唤起 + 轻松预约效率”。因此视觉 DNA 应该把夜色作为容器，而不是单纯做成黑暗模式：用石墨/岩石系深底营造深夜氛围，避免过度冰冷；卡片采用圆角大、半透明、轻玻璃质感，让界面像夜里灯下的桌面菜单，带有可接近性和人情味；主色选择偏暖的玫瑰色来传达食欲、热度与人气，辅以琥珀色作为食物与灯光联想，强化“夜宵/小酒馆”的诱引感。整体边界保持清晰但不过分锋利，确保预约流程的可信度与可读性，适合B2C场景中既要高效下单，又要让人产生“现在就想去”的冲动。玻璃轻模糊用于分层而非炫技，表示夜晚空间感与信息层次；阴影采用深而柔的策略，像柜台灯光下的浮起感，强化温暖而不显厚重。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -309,7 +309,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-stone-950","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"完成深夜食堂预约单\",\"steps\":[\"进入 /预约总览 -&gt; 选择可订门店 -&gt; 跳转 /新建预约 -&gt; 填写人数、时间、偏好 -&gt; 提交预约 -&gt; 成功提示与通知发送\"]},{\"id\":\"flow_2\",\"description\":\"门店确认并核销预约\",\"steps\":[\"进入 /预约详情 -&gt; 检查联系人与备注 -&gt; 前往 /到店核销 -&gt; 输入核销码 -&gt; 确认到店 -&gt; 更新状态为已履约\"]},{\"id\":\"flow_3\",\"description\":\"运营侧优化夜间时段\",\"steps\":[\"进入 /时段运营 -&gt; 查看热力图与取消趋势 -&gt; 调整容量与营业策略 -&gt; 发布时段变更 -&gt; 用户端收到消息通知\"]}]","visual_primaryColor":"amber-500","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/90 border border-stone-700 shadow-2xl","visual_reasoning":"深夜食堂在线预约单适合夜间氛围：用深色背景营造深夜、温暖、安静的用餐感受；琥珀色作为主色传达灯光与食欲；卡片与按钮保持中等圆角，兼顾亲切感和效率，适合预约这种高频、信息密度中等的服务场景。","lang":"ZH","visual_buttonClass":"rounded-xl bg-amber-500 text-stone-950 font-semibold shadow-lg hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED: [\n  \"flow_1（完成深夜预约）: 步骤要求为“预约总览 -&gt; 在线预约单 -&gt; 填写人数与时间 -&gt; 提交预约 -&gt; 预约成功页”，但页面之间没有真实可达的 #hash 流转链路。虽然存在 #flow_1 / #pg3-submit / #pg3-success / #pg4-success 等锚点文字，但缺少明确从“预约总览”进入“在线预约单”的可执行链接，以及“填写人数与时间”对应的独立页面/步骤页。\",\n  \"flow_1: 预约成功页缺失。代码中多处链接指向 #pg3-success、#pg4-success，但 HTML 中没有对应的 #pg3-success 或 #pg4-success 页面内容。\",\n  \"flow_2（提前预点夜宵）: 步骤要求为“预约总览 -&gt; 菜单与加购 -&gt; 选择菜品 -&gt; 确认加购 -&gt; 预约确认页”，但“选择菜品”与“确认加购”没有独立的可遍历页面/步骤页，主要只是列表按钮；且“预约确认页”虽在部分位置写有文案，但缺少稳定对应的唯一页面锚点闭环。\",\n  \"flow_2: 多处“菜单与加购/确认加购”按钮仅指向同一页面内的 flow 锚点或当前页，缺少从“选择菜品”到“确认加购”再到“预约确认页”的清晰逐步跳转链路。\",\n  \"flow_3（门店处理高峰预约）: 步骤要求为“门店运营 -&gt; 查看预约队列 -&gt; 自动分配座位 -&gt; 扫码核销 -&gt; 到店成功提示”，但“自动分配座位”“扫码核销”“到店成功提示”没有形成明确、连续的页面跳转链路；大量按钮仅指向 #flow_3 或同页标签，缺少独立步骤页。\",\n  \"flow_3: 页面中存在 #pg3-checkin / #pg4-checkin / #pg3-verify 等引用，但没有完整且一致的“到店成功提示”落地页面锚点。\",\n  \"flow_4（处理迟到与释放座位）: 步骤要求为“门店运营 -&gt; 识别超时未到 -&gt; 标记迟到 -&gt; 释放座位 -&gt; 通知候补顾客”，但页面仅有“迟到与取消提醒/释放座位”相关文案与按钮，缺少“识别超时未到”“标记迟到”“通知候补顾客”的独立可遍历页面或明确跳转路径。\",\n  \"flow_4: 存在多个迟到/释放座位入口，但没有从门店运营页到该流程每一步的明确 #hash 链路，导致任务流不可完整验证。\",\n  \"全局问题: 该原型包含多个重复/并列页面段（#pg1, #pg2, #pg3, #pg4, #pg5, #pg6），但任务流要求的关键节点（如填写人数与时间、选择菜品、自动分配座位、扫码核销、到店成功提示、标记迟到、通知候补顾客）大多没有对应的独立步骤页或一致的锚点命名，导致核心任务流不可严格按步骤遍历。\"\n]"}</t>
+          <t>{"visual_bgClass":"bg-stone-950/90","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"用户完成深夜预约\",\"steps\":[\"预约首页 -&gt; 门店详情 -&gt; 预约确认 -&gt; 订单详情 -&gt; 成功\"]},{\"id\":\"flow_2\",\"description\":\"用户候补转正并到店核销\",\"steps\":[\"我的预约 -&gt; 候补中状态 -&gt; 转正通知 -&gt; 订单详情 -&gt; 二维码核销成功\"]},{\"id\":\"flow_3\",\"description\":\"用户改签预约时段\",\"steps\":[\"我的预约 -&gt; 预约详情 -&gt; 选择新时段 -&gt; 重新确认 -&gt; 改签成功\"]},{\"id\":\"flow_4\",\"description\":\"商家管理深夜高峰桌位\",\"steps\":[\"商家后台/门店运营 -&gt; 时段容量调整 -&gt; 临时加座 -&gt; 订单管理 -&gt; 实时生效\"]}]","visual_primaryColor":"rose-400","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/80 border border-white/10 rounded-3xl shadow-[0_20px_50px_rgba(0,0,0,0.3)]","visual_reasoning":"深夜食堂在线预约单的核心心理不是“冷酷科技”，而是“夜间安心感 + 食欲唤起 + 轻松预约效率”。因此视觉 DNA 应该把夜色作为容器，而不是单纯做成黑暗模式：用石墨/岩石系深底营造深夜氛围，避免过度冰冷；卡片采用圆角大、半透明、轻玻璃质感，让界面像夜里灯下的桌面菜单，带有可接近性和人情味；主色选择偏暖的玫瑰色来传达食欲、热度与人气，辅以琥珀色作为食物与灯光联想，强化“夜宵/小酒馆”的诱引感。整体边界保持清晰但不过分锋利，确保预约流程的可信度与可读性，适合B2C场景中既要高效下单，又要让人产生“现在就想去”的冲动。玻璃轻模糊用于分层而非炫技，表示夜晚空间感与信息层次；阴影采用深而柔的策略，像柜台灯光下的浮起感，强化温暖而不显厚重。","lang":"ZH","visual_buttonClass":"rounded-xl bg-amber-500 text-stone-950 font-semibold shadow-lg hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n- flow_1: “预约首页 -&gt; 在线预约页”有入口，但“在线预约页 -&gt; 填写人数与时间 -&gt; 订单确认页 -&gt; 支付定金 -&gt; 预约成功页”不够完整可遍历。`#pg1-booking` 里只有“去订单确认页 / 支付定金后成功页”，缺少明确的“填写人数与时间”提交动作；且“支付定金”没有明确从订单确认页继续到成功页的可操作提交按钮链路。  \n- flow_2: “预约成功页 -&gt; 点击改签 -&gt; 在线预约页”在 `#pg1-success` 有“点击改签”，但后续“在线预约页 -&gt; 重新选择时间 -&gt; 订单确认页 -&gt; 更新成功提示”缺少明确的“重新选择时间”提交/确认动作与“更新成功提示”页面/按钮链路，且成功提示文案与页面跳转不一致。  \n- flow_3: “管理看板 -&gt; 预约管理页”存在入口，但“筛选高峰时段订单 -&gt; 分配桌位 -&gt; 标记确认 -&gt; 更新实时状态”中，`#pg6` 的“分配桌位”“标记确认并同步状态”是按钮样式但没有对应 hash 跳转或可验证的完成页/状态页；另外 `#pg5`/`#pg6` 对“管理看板”与“预约管理页”的命名和跳转关系混乱，无法确认从看板到管理页的单一路径。  \n- flow_4: “管理看板 -&gt; 查看风险列表 -&gt; 打开顾客详情 -&gt; 发送提醒消息 -&gt; 调整桌位预留 -&gt; 结果记录”不完整。虽然有“风险列表”入口和弹窗详情，但“发送提醒消息”“调整桌位预留”“结果记录”缺少明确的可遍历提交/确认路径或结果页面；部分按钮只是静态按钮，没有链接到目标步骤。  \n- 页面/锚点命名混乱：`#pg5` 标题为“预约管理”，但页面内又出现“返回管理看板 / 去在线预约页 / 订单确认页”等与 flow 定义不一致的导航；`#pg6` 标题为“数据看板”，却承载大量预约管理内容，导致任务流中的“管理看板 / 预约管理页 / 查看风险列表”等页面对应不清晰。  \n- 缺失明确“更新成功提示 / 结果记录”页面：任务流要求的最终反馈页在 prototype 中没有独立、明确、可跳转验证的目标。","visual_accentColor":"amber-300","visual_shadowStrategy":"shadow-[0_20px_50px_rgba(0,0,0,0.3)]","visual_borderAccent":"border-white/10","visual_glassIntensity":"backdrop-blur-md"}</t>
         </is>
       </c>
     </row>
@@ -321,7 +321,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>精酿啤酒评分系统适合偏夜店/酒吧式的深色氛围，能突出品鉴、醇厚、专业感；琥珀色作为主色联想到酒液与麦芽，配合较高密度布局，便于快速记录风味维度与评分。</t>
+          <t>精酿啤酒口味评分系统的核心心理不是冷冰冰的工具感，而是“品鉴、发现、记录、分享”的体验感。因此视觉上应该传达一种带有酒吧氛围与专业评测并存的成熟气质：暖琥珀与深石材底色让人联想到麦芽、木桶和暗色玻璃杯，既呼应精酿的风味层次，也能营造可靠、沉稳的评分环境。界面不宜过度花哨，否则会削弱评分的专业性；所以采用偏 Solid Paper 的结构语言，通过清晰边界、适度阴影和中等圆角来确保信息密度与可读性。主色选 amber，直接连接啤酒琥珀色泽与香气联想；辅色用 emerald 作为“新鲜度/品质/酒花感”的对比点，能在数据标签、评分高亮或风味徽章中形成清爽的识别。轻度毛玻璃可用于浮层和筛选面板，模拟酒吧灯光下的半透明感，但保持克制，避免影响评分列表的清晰度。整体气质应是“专业品鉴 + 温暖社交 + 轻微酒馆氛围”，既适合桌面端的高信息密度，也适合移动端快速打分与浏览。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -337,7 +337,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-stone-950","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"完成一次精酿啤酒评分\",\"steps\":[\"评分工作台 -&gt; 选择酒款 -&gt; 填写香气/苦度/酒体等评分 -&gt; 选择风味标签 -&gt; 保存评分 -&gt; 生成评分结果页\"]},{\"id\":\"flow_2\",\"description\":\"通过个人口味画像发现新酒款\",\"steps\":[\"风味画像 -&gt; 查看偏好总结 -&gt; 进入推荐发现 -&gt; 浏览推荐酒款 -&gt; 打开酒款详情 -&gt; 收藏或加入品鉴清单\"]},{\"id\":\"flow_3\",\"description\":\"对比多款精酿啤酒并做决策\",\"steps\":[\"酒款库 -&gt; 选择多款酒 -&gt; 进入对比页 -&gt; 查看风味差异与评分维度 -&gt; 输出对比结论 -&gt; 收藏优胜酒款\"]},{\"id\":\"flow_4\",\"description\":\"商家查看市场偏好分析\",\"steps\":[\"数据分析 -&gt; 选择时间范围与区域 -&gt; 查看评分趋势 -&gt; 分析风味偏好变化 -&gt; 导出报表 -&gt; 制定选品策略\"]}]","visual_primaryColor":"amber-500","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/80 border border-stone-700 shadow-xl shadow-black/20 backdrop-blur","visual_reasoning":"精酿啤酒评分系统适合偏夜店/酒吧式的深色氛围，能突出品鉴、醇厚、专业感；琥珀色作为主色联想到酒液与麦芽，配合较高密度布局，便于快速记录风味维度与评分。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-amber-500 text-stone-950 font-semibold hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED: [\n  \"flow_1: 虽然存在“口味总览 -&gt; 快速评分”链接，以及“提交评分 / 生成风味图谱”按钮，但“填写多维度评分与风味标签”这一关键步骤在交互上没有真正可填写的表单控件，只有静态展示/按钮，缺少明确的输入与提交动作闭环。\",\n  \"flow_1: “提交成功并生成风味图谱”在多个页面中只是跳转到锚点页面或预览区，没有明确从快速评分页直接到“提交成功/风味图谱”的可靠 hash 路径闭环；部分按钮指向的锚点页并不对应实际独立成功页。\",\n  \"flow_2: “口味总览 -&gt; 个人口味画像 -&gt; 个性推荐列表 -&gt; 查看酒款详情 -&gt; 加入收藏”路径不完整。虽然页面中有“个人口味画像”“个性推荐列表”“查看详情”“加入收藏”按钮，但多个按钮都仍指向同一 flow/页面锚点，而不是明确从总览页逐层跳转到对应详情页。\",\n  \"flow_2: “查看酒款详情”缺少明确可达的独立详情内容页面映射；部分链接仅指向 #pg2-detail、#beer-detail 等，但在主流程中并未形成从推荐列表到详情再到收藏的稳定、唯一可追踪路径。\",\n  \"flow_3: “风味图谱 -&gt; 选择风格筛选 -&gt; 多酒款横向对比 -&gt; 查看差异洞察 -&gt; 保存对比结果”存在部分缺口：虽然有“同风格对比/保存对比结果/查看差异洞察”按钮，但缺少真正的“风格筛选”交互控件，只有静态文案和卡片展示，没有可操作的筛选器。\",\n  \"flow_3: “多酒款横向对比”与“查看差异洞察”虽有相关内容区，但部分链接指向的锚点（如 #pg2-detail、#compare-detail）并未提供完整、清晰的对比结果落点，保存结果也多为跳转式占位。\",\n  \"flow_4: “商家洞察 -&gt; 查看评分总览与趋势 -&gt; 定位差评集中点 -&gt; 调整菜单与上新策略 -&gt; 复看优化效果”虽在页面中出现对应模块，但路径分散在多个不同 hash 版本（#pg2、#pg3、#pg4、#pg5、#pg6），没有一个稳定的单一路径可从商家洞察页连续走完。\",\n  \"flow_4: “调整菜单与上新策略”没有明确的提交/保存动作按钮，只看到建议列表与“菜单优化”展示，缺少执行优化策略的核心 action。\",\n  \"整体: 该原型包含大量重复且分散的页面版本，很多任务流依赖的页面锚点并非从当前页面逐步可达，存在明显的锚点碎片化与路径不唯一问题，导致任务流无法被严格验证为逻辑可遍历。\"\n]"}</t>
+          <t>{"visual_bgClass":"bg-amber-950/95","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"录入并完成单款精酿评分\",\"steps\":[\"啤酒库 -&gt; 选择酒款 -&gt; 品鉴评分 -&gt; 填写维度评分与笔记 -&gt; 保存 -&gt; 风味总览更新\"]},{\"id\":\"flow_2\",\"description\":\"盲测模式下进行客观品鉴\",\"steps\":[\"啤酒库 -&gt; 开启盲测 -&gt; 品鉴评分 -&gt; 仅展示匿名编号 -&gt; 提交评分 -&gt; 解盲后生成对照结果\"]},{\"id\":\"flow_3\",\"description\":\"对比两款精酿并输出偏好结论\",\"steps\":[\"啤酒库 -&gt; 勾选两款酒 -&gt; 对比分析 -&gt; 查看风味差异与评分差异 -&gt; 生成偏好结论 -&gt; 收藏对比报告\"]},{\"id\":\"flow_4\",\"description\":\"基于历史评分查看个性化推荐\",\"steps\":[\"风味总览 -&gt; 进入洞察中心 -&gt; 查看偏好画像 -&gt; 浏览推荐酒款 -&gt; 添加到待品鉴列表\"]}]","visual_primaryColor":"amber","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/90 border border-amber-800/40 rounded-2xl shadow-xl","visual_reasoning":"精酿啤酒口味评分系统的核心心理不是冷冰冰的工具感，而是“品鉴、发现、记录、分享”的体验感。因此视觉上应该传达一种带有酒吧氛围与专业评测并存的成熟气质：暖琥珀与深石材底色让人联想到麦芽、木桶和暗色玻璃杯，既呼应精酿的风味层次，也能营造可靠、沉稳的评分环境。界面不宜过度花哨，否则会削弱评分的专业性；所以采用偏 Solid Paper 的结构语言，通过清晰边界、适度阴影和中等圆角来确保信息密度与可读性。主色选 amber，直接连接啤酒琥珀色泽与香气联想；辅色用 emerald 作为“新鲜度/品质/酒花感”的对比点，能在数据标签、评分高亮或风味徽章中形成清爽的识别。轻度毛玻璃可用于浮层和筛选面板，模拟酒吧灯光下的半透明感，但保持克制，避免影响评分列表的清晰度。整体气质应是“专业品鉴 + 温暖社交 + 轻微酒馆氛围”，既适合桌面端的高信息密度，也适合移动端快速打分与浏览。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-amber-500 text-stone-950 font-semibold hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n1. `/dashboard -&gt; /tastings` is not actually implemented as a reachable page/route. The prototype only contains hash targets like `#pg2`, `#pg3`, etc., and there is no dedicated `#tastings` section or page. Multiple buttons point to `#tastings`, but no matching destination exists.  \n2. `/dashboard -&gt; /profile` is broken for the same reason: buttons point to `#profile`, but there is no `#profile` page/section in the prototype.  \n3. `/dashboard -&gt; /recommendations` is broken: buttons point to `#recommendations`, but there is no `#recommendations` page/section in the prototype.  \n4. `/dashboard -&gt; /insights` is broken: buttons point to `#insights`, but there is no `#insights` page/section in the prototype.  \n5. Flow 1 is missing the core “填写品鉴信息与多维评分” form interaction and the “保存记录” action. The prototype shows record cards and a detail drawer, but no input form, no submit/save button, and no explicit result-update action after saving.  \n6. Flow 2 is missing the “阅读偏好雷达图与风格阈值” and “查看推荐解释” in a dedicated `/profile` page; those elements exist under `#pg4`, but the requested route hash is absent and therefore not logically traversable as specified.  \n7. Flow 3 is missing the required “按匹配度筛选” interaction in a functional sense. The recommendations page contains explanatory text mentioning matching, but there is no actual filter control/UI to perform the筛选. It also lacks a clear “收藏目标啤酒” action button tied to the recommendation items; the page shows collection status labels, not a save/favorite action.  \n8. Flow 4 is missing the required “选择时间区间” control and the explicit “生成复盘结论” action. The insights content is static; there is no time-range selector or generation/submit control.","visual_accentColor":"emerald","visual_shadowStrategy":"shadow-[0_20px_50px_rgba(0,0,0,0.3)]","visual_borderAccent":"border-slate-800/50","visual_glassIntensity":"backdrop-blur-md"}</t>
         </is>
       </c>
     </row>

--- a/backend/STRESS_TEST_REPORT_200.xlsx
+++ b/backend/STRESS_TEST_REPORT_200.xlsx
@@ -265,7 +265,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>社区团购选品小程序的核心心理是“可信、清晰、效率优先”。它不是强情绪消费型产品，而是围绕团长、供应链和社区成员的高频决策工具，因此视觉上需要建立稳定、专业、低噪音的信任感。整体采用偏 slate/indigo 的深色中性色系，能传达供应链管理、数据判断和价格秩序感；卡片以 Solid Paper 为主，配合明确边界与适度阴影，强调信息分层和可扫读性，适合商品列表、规格对比、销量与库存状态等高密度内容。适度的玻璃模糊只作为辅助层，用于营造现代感和轻量层级，而不是喧宾夺主。翠绿作为点缀，天然对应“选品、上架、热卖、增长”这类正向操作反馈，同时也能强化生鲜、社区生活类商品的亲和力。整体气质应是“高效率的社区供给中枢”：既要让团长快速做出判断，也要让用户感到货源靠谱、价格透明、选择有序。</t>
+          <t>This interface should feel fast, trustworthy, and promotion-led, matching the high-density workflow of community group-buy product selection. A light slate background with clean white cards creates strong scanability for price, stock, sales volume, and social proof. Tight spacing, snug leading, and tracking-tight support discovery-density so users can compare deals quickly without visual fatigue. Subtle borders and soft shadow-sm provide structure for persistent top search, dynamic category navigation, and product grids without adding clutter. Emerald as the primary color signals freshness and commerce confidence, while orange works as a contrasting urgency accent for flash sales, countdowns, and hot deals. Sans typography is best for dense, operational browsing in a mini-program context, where speed and legibility matter more than editorial tone.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -281,7 +281,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-slate-950/95","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"爆品选品并发起团购\",\"steps\":[\"进入爆品推荐中心 -&gt; 查看社区热销榜 -&gt; 选择高毛利商品 -&gt; 加入选品清单 -&gt; 跳转团购活动配置 -&gt; 发布活动成功\"]},{\"id\":\"flow_2\",\"description\":\"批量筛选商品并完成上架\",\"steps\":[\"进入选品清单管理 -&gt; 设置价格带与品类筛选 -&gt; 对比商品销量与库存 -&gt; 批量加入清单 -&gt; 生成活动商品列表 -&gt; 上架完成\"]},{\"id\":\"flow_3\",\"description\":\"处理库存预警并替换商品\",\"steps\":[\"进入库存与履约监控 -&gt; 查看缺货预警列表 -&gt; 识别风险商品 -&gt; 返回选品清单管理 -&gt; 替换为可售商品 -&gt; 重新保存活动\"]},{\"id\":\"flow_4\",\"description\":\"活动结束后复盘优化\",\"steps\":[\"进入数据复盘分析 -&gt; 查看销量趋势与毛利分析 -&gt; 定位高转化商品 -&gt; 标记低效商品 -&gt; 生成下一轮选品建议\"]}]","visual_primaryColor":"indigo-500","visual_fontFamily":"font-sans","visual_cardClass":"bg-slate-900/80 border border-slate-800/60 rounded-2xl shadow-xl","visual_reasoning":"社区团购选品小程序的核心心理是“可信、清晰、效率优先”。它不是强情绪消费型产品，而是围绕团长、供应链和社区成员的高频决策工具，因此视觉上需要建立稳定、专业、低噪音的信任感。整体采用偏 slate/indigo 的深色中性色系，能传达供应链管理、数据判断和价格秩序感；卡片以 Solid Paper 为主，配合明确边界与适度阴影，强调信息分层和可扫读性，适合商品列表、规格对比、销量与库存状态等高密度内容。适度的玻璃模糊只作为辅助层，用于营造现代感和轻量层级，而不是喧宾夺主。翠绿作为点缀，天然对应“选品、上架、热卖、增长”这类正向操作反馈，同时也能强化生鲜、社区生活类商品的亲和力。整体气质应是“高效率的社区供给中枢”：既要让团长快速做出判断，也要让用户感到货源靠谱、价格透明、选择有序。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-emerald-600 text-white shadow-sm hover:bg-emerald-700","functional_audit_result":"CORRECTION_NEEDED: \n1. flow_1 / flow_2 / flow_3 / flow_4 all reference navigation into pages that are not actually traversable via matching hash links from the intended source pages:\n   - The sidebar links go to #pg1–#pg13, but the task flows require transitions like “进入选品中心 -&gt; 使用多维筛选条件 -&gt; 打开商品详情 -&gt; 加入选品清单 -&gt; 一键上架到团购池”.\n   - In several places the prototype uses placeholder hashes such as #drawer-open, #list-add, #group-buy-pool, #analytics-risk that do not correspond to real routed pages/sections with those IDs.\n\n2. flow_1 broken path:\n   - “打开商品详情” from 选品中心 exists only as click-to-open drawer behavior, but there is no hash link from 选品中心 to 商品详情 page/section as required by the audit rule.\n   - “加入选品清单” and “一键上架到团购池” appear as anchors, but many point to placeholder hashes or same-page placeholders rather than a concrete traversable route.\n   - The intended completion flow is not explicitly connected end-to-end with a stable hash path.\n\n3. flow_2 broken path:\n   - “查看智能推荐理由” is present on pg4, but the route to a distinct page/section for recommendation details is incomplete/inconsistent.\n   - “标记通过” / “淘汰” buttons exist in drawers, but they point to #drawer-open or same current hash instead of a dedicated actionable destination, so the evaluation flow is not logically traversable per hash-link rule.\n\n4. flow_3 broken path:\n   - “进入数据看板” exists, but “查看补货预警与滞销列表” and “打开商品详情” are not connected through a clear hash-based page sequence.\n   - “调整活动或补货建议” is shown as information, but there is no actionable button/link to a dedicated adjustment page or anchored workflow.\n   - “更新选品清单” exists, but again is not part of a fully linked end-to-end route.\n\n5. flow_4 broken path:\n   - “进入数据看板 -&gt; 选择品类或时间范围 -&gt; 查看供应商中心与商品表现 -&gt; 标记高风险供应商 -&gt; 优化后续选品策略” is only partially represented.\n   - There is no distinct, hash-addressable control for “标记高风险供应商”; current UI only displays supplier risk cards and generic strategy text.\n   - The “优化后续选品策略” action is informational, not a traversable action button tied to a destination.\n\n6. Data consistency issues:\n   - Several links reference pages/targets not defined by IDs in the DOM, causing the prototype to fail the hash-based traversal requirement.\n   - Some actions are duplicated as non-functional buttons in the global drawer and page content without a clear submit/complete step.\n\n","visual_accentColor":"emerald-400","visual_shadowStrategy":"shadow-xl","visual_borderAccent":"border-slate-800/50","visual_glassIntensity":"backdrop-blur-md"}</t>
+          <t>{"visual_bgClass":"bg-slate-50","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"首页爆款浏览到快速加购的高频选品闭环。\",\"steps\":[\"入口：用户进入首页查看促销轮播、爆款推荐或限时秒杀卡片\",\"行动：点击商品卡，查看详情后直接加入购物车并调整数量\",\"反馈：订单汇总底栏实时更新商品数、金额与预计节省，购物车数量角标同步变化\"]},{\"id\":\"flow_2\",\"description\":\"分类筛选到对比决策的低成本选品闭环。\",\"steps\":[\"入口：用户从动态分类侧栏进入蔬菜、水果或粮油调味分类\",\"行动：使用筛选抽屉按产地、价格、新鲜度和配送时间缩小范围，比较商品卡\",\"反馈：筛选结果即时刷新，卡片排序与库存标签同步变化，用户可直接批量加购\"]},{\"id\":\"flow_3\",\"description\":\"社交证明驱动的成交闭环。\",\"steps\":[\"入口：用户看到团长推荐、邻里购买数或倒计时促销提示进入商品详情\",\"行动：确认规格、查看评价摘要与优惠信息后提交订单\",\"反馈：弹出下单成功态，显示支付完成、预计送达时间与继续选购入口\"]}]","visual_primaryColor":"text-emerald-600","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-slate-100 bg-white/90 p-4 md:p-5","visual_reasoning":"This interface should feel fast, trustworthy, and promotion-led, matching the high-density workflow of community group-buy product selection. A light slate background with clean white cards creates strong scanability for price, stock, sales volume, and social proof. Tight spacing, snug leading, and tracking-tight support discovery-density so users can compare deals quickly without visual fatigue. Subtle borders and soft shadow-sm provide structure for persistent top search, dynamic category navigation, and product grids without adding clutter. Emerald as the primary color signals freshness and commerce confidence, while orange works as a contrasting urgency accent for flash sales, countdowns, and hot deals. Sans typography is best for dense, operational browsing in a mini-program context, where speed and legibility matter more than editorial tone.","lang":"ZH","visual_buttonClass":"rounded-2xl bg-emerald-600 text-white shadow-sm hover:bg-emerald-700","functional_audit_result":"CORRECTION_NEEDED: \n1. flow_1 / flow_2 / flow_3 / flow_4 all reference navigation into pages that are not actually traversable via matching hash links from the intended source pages:\n   - The sidebar links go to #pg1–#pg13, but the task flows require transitions like “进入选品中心 -&gt; 使用多维筛选条件 -&gt; 打开商品详情 -&gt; 加入选品清单 -&gt; 一键上架到团购池”.\n   - In several places the prototype uses placeholder hashes such as #drawer-open, #list-add, #group-buy-pool, #analytics-risk that do not correspond to real routed pages/sections with those IDs.\n\n2. flow_1 broken path:\n   - “打开商品详情” from 选品中心 exists only as click-to-open drawer behavior, but there is no hash link from 选品中心 to 商品详情 page/section as required by the audit rule.\n   - “加入选品清单” and “一键上架到团购池” appear as anchors, but many point to placeholder hashes or same-page placeholders rather than a concrete traversable route.\n   - The intended completion flow is not explicitly connected end-to-end with a stable hash path.\n\n3. flow_2 broken path:\n   - “查看智能推荐理由” is present on pg4, but the route to a distinct page/section for recommendation details is incomplete/inconsistent.\n   - “标记通过” / “淘汰” buttons exist in drawers, but they point to #drawer-open or same current hash instead of a dedicated actionable destination, so the evaluation flow is not logically traversable per hash-link rule.\n\n4. flow_3 broken path:\n   - “进入数据看板” exists, but “查看补货预警与滞销列表” and “打开商品详情” are not connected through a clear hash-based page sequence.\n   - “调整活动或补货建议” is shown as information, but there is no actionable button/link to a dedicated adjustment page or anchored workflow.\n   - “更新选品清单” exists, but again is not part of a fully linked end-to-end route.\n\n5. flow_4 broken path:\n   - “进入数据看板 -&gt; 选择品类或时间范围 -&gt; 查看供应商中心与商品表现 -&gt; 标记高风险供应商 -&gt; 优化后续选品策略” is only partially represented.\n   - There is no distinct, hash-addressable control for “标记高风险供应商”; current UI only displays supplier risk cards and generic strategy text.\n   - The “优化后续选品策略” action is informational, not a traversable action button tied to a destination.\n\n6. Data consistency issues:\n   - Several links reference pages/targets not defined by IDs in the DOM, causing the prototype to fail the hash-based traversal requirement.\n   - Some actions are duplicated as non-functional buttons in the global drawer and page content without a clear submit/complete step.\n\n","visual_accentColor":"text-orange-500","visual_shadowStrategy":"shadow-sm","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-snug","visual_letterSpacing":"tracking-tight","visual_serifBias":"false"}</t>
         </is>
       </c>
     </row>
@@ -293,7 +293,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>深夜食堂在线预约单的核心心理不是“冷酷科技”，而是“夜间安心感 + 食欲唤起 + 轻松预约效率”。因此视觉 DNA 应该把夜色作为容器，而不是单纯做成黑暗模式：用石墨/岩石系深底营造深夜氛围，避免过度冰冷；卡片采用圆角大、半透明、轻玻璃质感，让界面像夜里灯下的桌面菜单，带有可接近性和人情味；主色选择偏暖的玫瑰色来传达食欲、热度与人气，辅以琥珀色作为食物与灯光联想，强化“夜宵/小酒馆”的诱引感。整体边界保持清晰但不过分锋利，确保预约流程的可信度与可读性，适合B2C场景中既要高效下单，又要让人产生“现在就想去”的冲动。玻璃轻模糊用于分层而非炫技，表示夜晚空间感与信息层次；阴影采用深而柔的策略，像柜台灯光下的浮起感，强化温暖而不显厚重。</t>
+          <t>深夜食堂预约场景的核心不是高效率的信息密度，而是“即时安抚 + 低门槛预订 + 夜间氛围感”。因此整体采用深色夜间底色来建立深夜语境与安静感，用琥珀色作为少量高对比强调，承载‘可订位’、‘确认’、‘营业中’等关键动作提示，帮助用户在夜间快速决策。卡片采用中等密度的容器样式，兼顾表单填写的清晰性与门店信息、环境图、可订时段等辅助模块的分区感，符合固定顶部导航 + 动态侧栏的布局策略。字体选择无衬线以提高表单与状态信息的可读性，行高和字距偏紧以适配预约任务流的短路径浏览，整体传达稳、暖、可信、可立即完成预约的体验。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -309,7 +309,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-stone-950/90","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"用户完成深夜预约\",\"steps\":[\"预约首页 -&gt; 门店详情 -&gt; 预约确认 -&gt; 订单详情 -&gt; 成功\"]},{\"id\":\"flow_2\",\"description\":\"用户候补转正并到店核销\",\"steps\":[\"我的预约 -&gt; 候补中状态 -&gt; 转正通知 -&gt; 订单详情 -&gt; 二维码核销成功\"]},{\"id\":\"flow_3\",\"description\":\"用户改签预约时段\",\"steps\":[\"我的预约 -&gt; 预约详情 -&gt; 选择新时段 -&gt; 重新确认 -&gt; 改签成功\"]},{\"id\":\"flow_4\",\"description\":\"商家管理深夜高峰桌位\",\"steps\":[\"商家后台/门店运营 -&gt; 时段容量调整 -&gt; 临时加座 -&gt; 订单管理 -&gt; 实时生效\"]}]","visual_primaryColor":"rose-400","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/80 border border-white/10 rounded-3xl shadow-[0_20px_50px_rgba(0,0,0,0.3)]","visual_reasoning":"深夜食堂在线预约单的核心心理不是“冷酷科技”，而是“夜间安心感 + 食欲唤起 + 轻松预约效率”。因此视觉 DNA 应该把夜色作为容器，而不是单纯做成黑暗模式：用石墨/岩石系深底营造深夜氛围，避免过度冰冷；卡片采用圆角大、半透明、轻玻璃质感，让界面像夜里灯下的桌面菜单，带有可接近性和人情味；主色选择偏暖的玫瑰色来传达食欲、热度与人气，辅以琥珀色作为食物与灯光联想，强化“夜宵/小酒馆”的诱引感。整体边界保持清晰但不过分锋利，确保预约流程的可信度与可读性，适合B2C场景中既要高效下单，又要让人产生“现在就想去”的冲动。玻璃轻模糊用于分层而非炫技，表示夜晚空间感与信息层次；阴影采用深而柔的策略，像柜台灯光下的浮起感，强化温暖而不显厚重。","lang":"ZH","visual_buttonClass":"rounded-xl bg-amber-500 text-stone-950 font-semibold shadow-lg hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n- flow_1: “预约首页 -&gt; 在线预约页”有入口，但“在线预约页 -&gt; 填写人数与时间 -&gt; 订单确认页 -&gt; 支付定金 -&gt; 预约成功页”不够完整可遍历。`#pg1-booking` 里只有“去订单确认页 / 支付定金后成功页”，缺少明确的“填写人数与时间”提交动作；且“支付定金”没有明确从订单确认页继续到成功页的可操作提交按钮链路。  \n- flow_2: “预约成功页 -&gt; 点击改签 -&gt; 在线预约页”在 `#pg1-success` 有“点击改签”，但后续“在线预约页 -&gt; 重新选择时间 -&gt; 订单确认页 -&gt; 更新成功提示”缺少明确的“重新选择时间”提交/确认动作与“更新成功提示”页面/按钮链路，且成功提示文案与页面跳转不一致。  \n- flow_3: “管理看板 -&gt; 预约管理页”存在入口，但“筛选高峰时段订单 -&gt; 分配桌位 -&gt; 标记确认 -&gt; 更新实时状态”中，`#pg6` 的“分配桌位”“标记确认并同步状态”是按钮样式但没有对应 hash 跳转或可验证的完成页/状态页；另外 `#pg5`/`#pg6` 对“管理看板”与“预约管理页”的命名和跳转关系混乱，无法确认从看板到管理页的单一路径。  \n- flow_4: “管理看板 -&gt; 查看风险列表 -&gt; 打开顾客详情 -&gt; 发送提醒消息 -&gt; 调整桌位预留 -&gt; 结果记录”不完整。虽然有“风险列表”入口和弹窗详情，但“发送提醒消息”“调整桌位预留”“结果记录”缺少明确的可遍历提交/确认路径或结果页面；部分按钮只是静态按钮，没有链接到目标步骤。  \n- 页面/锚点命名混乱：`#pg5` 标题为“预约管理”，但页面内又出现“返回管理看板 / 去在线预约页 / 订单确认页”等与 flow 定义不一致的导航；`#pg6` 标题为“数据看板”，却承载大量预约管理内容，导致任务流中的“管理看板 / 预约管理页 / 查看风险列表”等页面对应不清晰。  \n- 缺失明确“更新成功提示 / 结果记录”页面：任务流要求的最终反馈页在 prototype 中没有独立、明确、可跳转验证的目标。","visual_accentColor":"amber-300","visual_shadowStrategy":"shadow-[0_20px_50px_rgba(0,0,0,0.3)]","visual_borderAccent":"border-white/10","visual_glassIntensity":"backdrop-blur-md"}</t>
+          <t>{"visual_bgClass":"bg-slate-950","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"用户从首页快速发现可订位时段，并提交预约完成确认闭环。\",\"steps\":[\"ENTRY：首页推荐预约时段卡\",\"ACTION：选择日期、时间、人数并提交手机号\",\"FEEDBACK：展示预约成功页、预约编号与短信通知说明\"]},{\"id\":\"flow_2\",\"description\":\"用户先查看门店详情与氛围，再进入预约表单完成订位。\",\"steps\":[\"ENTRY：门店详情页的实时余位提示\",\"ACTION：查看交通、营业时间后点击预约按钮并填写表单\",\"FEEDBACK：表单提交后跳转预约确认页并展示到店提醒入口\"]},{\"id\":\"flow_3\",\"description\":\"用户在个人中心管理已有预约，完成改期或取消后获得状态更新。\",\"steps\":[\"ENTRY：我的预约页的当前订单卡片\",\"ACTION：点击改期或取消并确认操作\",\"FEEDBACK：页面状态更新、通知中心出现变更消息\"]}]","visual_primaryColor":"slate","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-slate-800 bg-slate-900/90 p-5 md:p-6","visual_reasoning":"深夜食堂预约场景的核心不是高效率的信息密度，而是“即时安抚 + 低门槛预订 + 夜间氛围感”。因此整体采用深色夜间底色来建立深夜语境与安静感，用琥珀色作为少量高对比强调，承载‘可订位’、‘确认’、‘营业中’等关键动作提示，帮助用户在夜间快速决策。卡片采用中等密度的容器样式，兼顾表单填写的清晰性与门店信息、环境图、可订时段等辅助模块的分区感，符合固定顶部导航 + 动态侧栏的布局策略。字体选择无衬线以提高表单与状态信息的可读性，行高和字距偏紧以适配预约任务流的短路径浏览，整体传达稳、暖、可信、可立即完成预约的体验。","lang":"ZH","visual_buttonClass":"rounded-xl bg-amber-500 text-stone-950 font-semibold shadow-lg hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n- flow_1: “预约首页 -&gt; 在线预约页”有入口，但“在线预约页 -&gt; 填写人数与时间 -&gt; 订单确认页 -&gt; 支付定金 -&gt; 预约成功页”不够完整可遍历。`#pg1-booking` 里只有“去订单确认页 / 支付定金后成功页”，缺少明确的“填写人数与时间”提交动作；且“支付定金”没有明确从订单确认页继续到成功页的可操作提交按钮链路。  \n- flow_2: “预约成功页 -&gt; 点击改签 -&gt; 在线预约页”在 `#pg1-success` 有“点击改签”，但后续“在线预约页 -&gt; 重新选择时间 -&gt; 订单确认页 -&gt; 更新成功提示”缺少明确的“重新选择时间”提交/确认动作与“更新成功提示”页面/按钮链路，且成功提示文案与页面跳转不一致。  \n- flow_3: “管理看板 -&gt; 预约管理页”存在入口，但“筛选高峰时段订单 -&gt; 分配桌位 -&gt; 标记确认 -&gt; 更新实时状态”中，`#pg6` 的“分配桌位”“标记确认并同步状态”是按钮样式但没有对应 hash 跳转或可验证的完成页/状态页；另外 `#pg5`/`#pg6` 对“管理看板”与“预约管理页”的命名和跳转关系混乱，无法确认从看板到管理页的单一路径。  \n- flow_4: “管理看板 -&gt; 查看风险列表 -&gt; 打开顾客详情 -&gt; 发送提醒消息 -&gt; 调整桌位预留 -&gt; 结果记录”不完整。虽然有“风险列表”入口和弹窗详情，但“发送提醒消息”“调整桌位预留”“结果记录”缺少明确的可遍历提交/确认路径或结果页面；部分按钮只是静态按钮，没有链接到目标步骤。  \n- 页面/锚点命名混乱：`#pg5` 标题为“预约管理”，但页面内又出现“返回管理看板 / 去在线预约页 / 订单确认页”等与 flow 定义不一致的导航；`#pg6` 标题为“数据看板”，却承载大量预约管理内容，导致任务流中的“管理看板 / 预约管理页 / 查看风险列表”等页面对应不清晰。  \n- 缺失明确“更新成功提示 / 结果记录”页面：任务流要求的最终反馈页在 prototype 中没有独立、明确、可跳转验证的目标。","visual_accentColor":"amber","visual_shadowStrategy":"shadow-xl","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-snug","visual_letterSpacing":"tracking-tight","visual_serifBias":"false"}</t>
         </is>
       </c>
     </row>
@@ -321,7 +321,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>精酿啤酒口味评分系统的核心心理不是冷冰冰的工具感，而是“品鉴、发现、记录、分享”的体验感。因此视觉上应该传达一种带有酒吧氛围与专业评测并存的成熟气质：暖琥珀与深石材底色让人联想到麦芽、木桶和暗色玻璃杯，既呼应精酿的风味层次，也能营造可靠、沉稳的评分环境。界面不宜过度花哨，否则会削弱评分的专业性；所以采用偏 Solid Paper 的结构语言，通过清晰边界、适度阴影和中等圆角来确保信息密度与可读性。主色选 amber，直接连接啤酒琥珀色泽与香气联想；辅色用 emerald 作为“新鲜度/品质/酒花感”的对比点，能在数据标签、评分高亮或风味徽章中形成清爽的识别。轻度毛玻璃可用于浮层和筛选面板，模拟酒吧灯光下的半透明感，但保持克制，避免影响评分列表的清晰度。整体气质应是“专业品鉴 + 温暖社交 + 轻微酒馆氛围”，既适合桌面端的高信息密度，也适合移动端快速打分与浏览。</t>
+          <t>该平台的核心是“感官探索 + 社群共识 + 口味可视化反馈”，因此视觉上应建立可信、专业但不冰冷的啤酒评鉴氛围。背景采用温润的 stone 系列，能承接酒液、麦芽与发酵质感；卡片使用白底微透与细边框，适合 12 栅格下的多模块并列信息，兼顾酒款详情、评分维度、评论流与推荐位的可读性。整体信息密度保持中等，使用 relaxed 行高与 normal 字距，确保专业参数、风味标签与社群内容都能被快速扫读。主色选择 amber，呼应麦芽与啤酒液体色泽，适合作为评分、关键数值和状态提示；辅色 emerald 用于“收藏 / 想喝 / 已喝”与推荐关联，强化探索与正反馈。阴影仅用轻量 shadow-sm，避免社交内容与专业数据区域之间产生过度层级干扰；同时启用轻度玻璃感以增强层次，但不削弱信息清晰度。字体维持 sans，可更好承载多维评分、风味轮与列表密度，符合 persistent top + dynamic sidebar 的结构需求。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -337,7 +337,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-amber-950/95","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"录入并完成单款精酿评分\",\"steps\":[\"啤酒库 -&gt; 选择酒款 -&gt; 品鉴评分 -&gt; 填写维度评分与笔记 -&gt; 保存 -&gt; 风味总览更新\"]},{\"id\":\"flow_2\",\"description\":\"盲测模式下进行客观品鉴\",\"steps\":[\"啤酒库 -&gt; 开启盲测 -&gt; 品鉴评分 -&gt; 仅展示匿名编号 -&gt; 提交评分 -&gt; 解盲后生成对照结果\"]},{\"id\":\"flow_3\",\"description\":\"对比两款精酿并输出偏好结论\",\"steps\":[\"啤酒库 -&gt; 勾选两款酒 -&gt; 对比分析 -&gt; 查看风味差异与评分差异 -&gt; 生成偏好结论 -&gt; 收藏对比报告\"]},{\"id\":\"flow_4\",\"description\":\"基于历史评分查看个性化推荐\",\"steps\":[\"风味总览 -&gt; 进入洞察中心 -&gt; 查看偏好画像 -&gt; 浏览推荐酒款 -&gt; 添加到待品鉴列表\"]}]","visual_primaryColor":"amber","visual_fontFamily":"font-sans","visual_cardClass":"bg-stone-900/90 border border-amber-800/40 rounded-2xl shadow-xl","visual_reasoning":"精酿啤酒口味评分系统的核心心理不是冷冰冰的工具感，而是“品鉴、发现、记录、分享”的体验感。因此视觉上应该传达一种带有酒吧氛围与专业评测并存的成熟气质：暖琥珀与深石材底色让人联想到麦芽、木桶和暗色玻璃杯，既呼应精酿的风味层次，也能营造可靠、沉稳的评分环境。界面不宜过度花哨，否则会削弱评分的专业性；所以采用偏 Solid Paper 的结构语言，通过清晰边界、适度阴影和中等圆角来确保信息密度与可读性。主色选 amber，直接连接啤酒琥珀色泽与香气联想；辅色用 emerald 作为“新鲜度/品质/酒花感”的对比点，能在数据标签、评分高亮或风味徽章中形成清爽的识别。轻度毛玻璃可用于浮层和筛选面板，模拟酒吧灯光下的半透明感，但保持克制，避免影响评分列表的清晰度。整体气质应是“专业品鉴 + 温暖社交 + 轻微酒馆氛围”，既适合桌面端的高信息密度，也适合移动端快速打分与浏览。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-amber-500 text-stone-950 font-semibold hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n1. `/dashboard -&gt; /tastings` is not actually implemented as a reachable page/route. The prototype only contains hash targets like `#pg2`, `#pg3`, etc., and there is no dedicated `#tastings` section or page. Multiple buttons point to `#tastings`, but no matching destination exists.  \n2. `/dashboard -&gt; /profile` is broken for the same reason: buttons point to `#profile`, but there is no `#profile` page/section in the prototype.  \n3. `/dashboard -&gt; /recommendations` is broken: buttons point to `#recommendations`, but there is no `#recommendations` page/section in the prototype.  \n4. `/dashboard -&gt; /insights` is broken: buttons point to `#insights`, but there is no `#insights` page/section in the prototype.  \n5. Flow 1 is missing the core “填写品鉴信息与多维评分” form interaction and the “保存记录” action. The prototype shows record cards and a detail drawer, but no input form, no submit/save button, and no explicit result-update action after saving.  \n6. Flow 2 is missing the “阅读偏好雷达图与风格阈值” and “查看推荐解释” in a dedicated `/profile` page; those elements exist under `#pg4`, but the requested route hash is absent and therefore not logically traversable as specified.  \n7. Flow 3 is missing the required “按匹配度筛选” interaction in a functional sense. The recommendations page contains explanatory text mentioning matching, but there is no actual filter control/UI to perform the筛选. It also lacks a clear “收藏目标啤酒” action button tied to the recommendation items; the page shows collection status labels, not a save/favorite action.  \n8. Flow 4 is missing the required “选择时间区间” control and the explicit “生成复盘结论” action. The insights content is static; there is no time-range selector or generation/submit control.","visual_accentColor":"emerald","visual_shadowStrategy":"shadow-[0_20px_50px_rgba(0,0,0,0.3)]","visual_borderAccent":"border-slate-800/50","visual_glassIntensity":"backdrop-blur-md"}</t>
+          <t>{"visual_bgClass":"bg-stone-50","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"从首页发现酒款并完成首次评分反馈闭环。\",\"steps\":[\"ENTRY：首页热门酒款卡片点击\",\"ACTION：进入酒款详情页，查看风味标签、评分分布并提交多维评分与短评\",\"FEEDBACK：评分立即刷新为个人已评分状态，社区均值与趋势图更新，并出现提交成功提示\"]},{\"id\":\"flow_2\",\"description\":\"从搜索进入目标酒款后记录喝后感并沉淀到个人口味档案。\",\"steps\":[\"ENTRY：顶部搜索框搜索酒款名称或风味标签\",\"ACTION：打开目标酒款详情，添加评论、上传图片、标记喝过状态\",\"FEEDBACK：评论出现在详情页与个人主页评分历史中，喝过统计同步增加\"]},{\"id\":\"flow_3\",\"description\":\"通过社区共识发现相似酒款并持续探索。\",\"steps\":[\"ENTRY：社区推荐页点击高分短评或热门讨论酒款\",\"ACTION：查看详情后点击相似推荐列表中的其他酒款继续浏览\",\"FEEDBACK：推荐列表根据浏览与评分实时调整，形成连续探索路径与偏好强化\"]}]","visual_primaryColor":"amber-600","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-slate-100 bg-white/90 p-5 md:p-6","visual_reasoning":"该平台的核心是“感官探索 + 社群共识 + 口味可视化反馈”，因此视觉上应建立可信、专业但不冰冷的啤酒评鉴氛围。背景采用温润的 stone 系列，能承接酒液、麦芽与发酵质感；卡片使用白底微透与细边框，适合 12 栅格下的多模块并列信息，兼顾酒款详情、评分维度、评论流与推荐位的可读性。整体信息密度保持中等，使用 relaxed 行高与 normal 字距，确保专业参数、风味标签与社群内容都能被快速扫读。主色选择 amber，呼应麦芽与啤酒液体色泽，适合作为评分、关键数值和状态提示；辅色 emerald 用于“收藏 / 想喝 / 已喝”与推荐关联，强化探索与正反馈。阴影仅用轻量 shadow-sm，避免社交内容与专业数据区域之间产生过度层级干扰；同时启用轻度玻璃感以增强层次，但不削弱信息清晰度。字体维持 sans，可更好承载多维评分、风味轮与列表密度，符合 persistent top + dynamic sidebar 的结构需求。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-amber-500 text-stone-950 font-semibold hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n1. `/dashboard -&gt; /tastings` is not actually implemented as a reachable page/route. The prototype only contains hash targets like `#pg2`, `#pg3`, etc., and there is no dedicated `#tastings` section or page. Multiple buttons point to `#tastings`, but no matching destination exists.  \n2. `/dashboard -&gt; /profile` is broken for the same reason: buttons point to `#profile`, but there is no `#profile` page/section in the prototype.  \n3. `/dashboard -&gt; /recommendations` is broken: buttons point to `#recommendations`, but there is no `#recommendations` page/section in the prototype.  \n4. `/dashboard -&gt; /insights` is broken: buttons point to `#insights`, but there is no `#insights` page/section in the prototype.  \n5. Flow 1 is missing the core “填写品鉴信息与多维评分” form interaction and the “保存记录” action. The prototype shows record cards and a detail drawer, but no input form, no submit/save button, and no explicit result-update action after saving.  \n6. Flow 2 is missing the “阅读偏好雷达图与风格阈值” and “查看推荐解释” in a dedicated `/profile` page; those elements exist under `#pg4`, but the requested route hash is absent and therefore not logically traversable as specified.  \n7. Flow 3 is missing the required “按匹配度筛选” interaction in a functional sense. The recommendations page contains explanatory text mentioning matching, but there is no actual filter control/UI to perform the筛选. It also lacks a clear “收藏目标啤酒” action button tied to the recommendation items; the page shows collection status labels, not a save/favorite action.  \n8. Flow 4 is missing the required “选择时间区间” control and the explicit “生成复盘结论” action. The insights content is static; there is no time-range selector or generation/submit control.","visual_accentColor":"emerald-500","visual_shadowStrategy":"shadow-sm","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-relaxed","visual_letterSpacing":"tracking-normal","visual_serifBias":"false"}</t>
         </is>
       </c>
     </row>

--- a/backend/STRESS_TEST_REPORT_200.xlsx
+++ b/backend/STRESS_TEST_REPORT_200.xlsx
@@ -93,127 +93,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="twoCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2667000" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2667000" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="true"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2667000" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -265,7 +146,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>This interface should feel fast, trustworthy, and promotion-led, matching the high-density workflow of community group-buy product selection. A light slate background with clean white cards creates strong scanability for price, stock, sales volume, and social proof. Tight spacing, snug leading, and tracking-tight support discovery-density so users can compare deals quickly without visual fatigue. Subtle borders and soft shadow-sm provide structure for persistent top search, dynamic category navigation, and product grids without adding clutter. Emerald as the primary color signals freshness and commerce confidence, while orange works as a contrasting urgency accent for flash sales, countdowns, and hot deals. Sans typography is best for dense, operational browsing in a mini-program context, where speed and legibility matter more than editorial tone.</t>
+          <t>该场景属于高频低客单的社区熟人信任交易，核心目标不是沉浸浏览，而是快速发现爆品、建立信任、迅速下单履约。因此整体视觉采用高密度信息架构：浅灰背景降低噪音，白色卡片承载商品信息以提高扫读效率；紧凑的 padding、较短行高与紧字距适配高频比较和快速决策。主色选择低存在感的 slate，保证商品图片、价格和库存状态成为第一视觉焦点；accent 使用 orange 强化‘到手价/立即拼团/限时抢购’等转化动作。阴影仅用轻量 shadow-sm，避免电商感过重导致界面松散；边框采用浅灰细线，适合 2-4 列响应式商品网格，清晰区分卡片但不过度分割。整体保持无玻璃拟态、无 serif 倾向、无冗余装饰，符合小程序轻量、快速、信任驱动的选品与履约闭环。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -281,7 +162,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-slate-50","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"首页爆款浏览到快速加购的高频选品闭环。\",\"steps\":[\"入口：用户进入首页查看促销轮播、爆款推荐或限时秒杀卡片\",\"行动：点击商品卡，查看详情后直接加入购物车并调整数量\",\"反馈：订单汇总底栏实时更新商品数、金额与预计节省，购物车数量角标同步变化\"]},{\"id\":\"flow_2\",\"description\":\"分类筛选到对比决策的低成本选品闭环。\",\"steps\":[\"入口：用户从动态分类侧栏进入蔬菜、水果或粮油调味分类\",\"行动：使用筛选抽屉按产地、价格、新鲜度和配送时间缩小范围，比较商品卡\",\"反馈：筛选结果即时刷新，卡片排序与库存标签同步变化，用户可直接批量加购\"]},{\"id\":\"flow_3\",\"description\":\"社交证明驱动的成交闭环。\",\"steps\":[\"入口：用户看到团长推荐、邻里购买数或倒计时促销提示进入商品详情\",\"行动：确认规格、查看评价摘要与优惠信息后提交订单\",\"反馈：弹出下单成功态，显示支付完成、预计送达时间与继续选购入口\"]}]","visual_primaryColor":"text-emerald-600","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-slate-100 bg-white/90 p-4 md:p-5","visual_reasoning":"This interface should feel fast, trustworthy, and promotion-led, matching the high-density workflow of community group-buy product selection. A light slate background with clean white cards creates strong scanability for price, stock, sales volume, and social proof. Tight spacing, snug leading, and tracking-tight support discovery-density so users can compare deals quickly without visual fatigue. Subtle borders and soft shadow-sm provide structure for persistent top search, dynamic category navigation, and product grids without adding clutter. Emerald as the primary color signals freshness and commerce confidence, while orange works as a contrasting urgency accent for flash sales, countdowns, and hot deals. Sans typography is best for dense, operational browsing in a mini-program context, where speed and legibility matter more than editorial tone.","lang":"ZH","visual_buttonClass":"rounded-2xl bg-emerald-600 text-white shadow-sm hover:bg-emerald-700","functional_audit_result":"CORRECTION_NEEDED: \n1. flow_1 / flow_2 / flow_3 / flow_4 all reference navigation into pages that are not actually traversable via matching hash links from the intended source pages:\n   - The sidebar links go to #pg1–#pg13, but the task flows require transitions like “进入选品中心 -&gt; 使用多维筛选条件 -&gt; 打开商品详情 -&gt; 加入选品清单 -&gt; 一键上架到团购池”.\n   - In several places the prototype uses placeholder hashes such as #drawer-open, #list-add, #group-buy-pool, #analytics-risk that do not correspond to real routed pages/sections with those IDs.\n\n2. flow_1 broken path:\n   - “打开商品详情” from 选品中心 exists only as click-to-open drawer behavior, but there is no hash link from 选品中心 to 商品详情 page/section as required by the audit rule.\n   - “加入选品清单” and “一键上架到团购池” appear as anchors, but many point to placeholder hashes or same-page placeholders rather than a concrete traversable route.\n   - The intended completion flow is not explicitly connected end-to-end with a stable hash path.\n\n3. flow_2 broken path:\n   - “查看智能推荐理由” is present on pg4, but the route to a distinct page/section for recommendation details is incomplete/inconsistent.\n   - “标记通过” / “淘汰” buttons exist in drawers, but they point to #drawer-open or same current hash instead of a dedicated actionable destination, so the evaluation flow is not logically traversable per hash-link rule.\n\n4. flow_3 broken path:\n   - “进入数据看板” exists, but “查看补货预警与滞销列表” and “打开商品详情” are not connected through a clear hash-based page sequence.\n   - “调整活动或补货建议” is shown as information, but there is no actionable button/link to a dedicated adjustment page or anchored workflow.\n   - “更新选品清单” exists, but again is not part of a fully linked end-to-end route.\n\n5. flow_4 broken path:\n   - “进入数据看板 -&gt; 选择品类或时间范围 -&gt; 查看供应商中心与商品表现 -&gt; 标记高风险供应商 -&gt; 优化后续选品策略” is only partially represented.\n   - There is no distinct, hash-addressable control for “标记高风险供应商”; current UI only displays supplier risk cards and generic strategy text.\n   - The “优化后续选品策略” action is informational, not a traversable action button tied to a destination.\n\n6. Data consistency issues:\n   - Several links reference pages/targets not defined by IDs in the DOM, causing the prototype to fail the hash-based traversal requirement.\n   - Some actions are duplicated as non-functional buttons in the global drawer and page content without a clear submit/complete step.\n\n","visual_accentColor":"text-orange-500","visual_shadowStrategy":"shadow-sm","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-snug","visual_letterSpacing":"tracking-tight","visual_serifBias":"false"}</t>
+          <t>{"visual_bgClass":"bg-slate-50","taskFlows":"[{\"id\":\"flow_home_to_cart\",\"description\":\"从首页发现爆品并快速加购，形成高频选品闭环。\",\"steps\":[\"入口：首页热销推荐卡 / 今日推荐区\",\"动作：点击商品卡查看价格、库存、起团状态后立即加购\",\"反馈：购物车角标更新、底部汇总金额刷新、出现已加入提示\"]},{\"id\":\"flow_category_to_detail_to_buy\",\"description\":\"从分类页筛选商品并通过详情弹窗完成决策。\",\"steps\":[\"入口：分类选品页动态分类侧栏\",\"动作：切换品类、使用筛选抽屉、打开商品详情并确认规格后加购\",\"反馈：详情弹窗关闭、列表库存扣减或状态更新、底栏应付金额变化\"]},{\"id\":\"flow_deal_to_success\",\"description\":\"从爆款促销页完成冲量购买并获得成交反馈。\",\"steps\":[\"入口：爆款与限时促销卡\",\"动作：查看团长推荐与倒计时后立即拼团/结算\",\"反馈：出现下单成功弹层、显示预计到货时间、可继续选购或查看订单\"]},{\"id\":\"flow_comment_reply\",\"description\":\"Users can enter a detail view, comment, reply, and see the thread update immediately.\",\"steps\":[\"ENTRY: Open the detail view from a discovery or content card\",\"ACTION: Add a comment or reply to an existing thread\",\"FEEDBACK: Comment thread updates instantly and interaction counts increase\"]},{\"id\":\"flow_return_to_feed\",\"description\":\"Users return from detail view back into the discovery/feed context without losing browsing continuity.\",\"steps\":[\"ENTRY: Open a detail view from the main discovery feed\",\"ACTION: Close the detail overlay or navigate back\",\"FEEDBACK: The user returns to the original feed context and can continue browsing\"]}]","visual_primaryColor":"slate","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-slate-100 bg-white/95 p-3 md:p-4","visual_reasoning":"该场景属于高频低客单的社区熟人信任交易，核心目标不是沉浸浏览，而是快速发现爆品、建立信任、迅速下单履约。因此整体视觉采用高密度信息架构：浅灰背景降低噪音，白色卡片承载商品信息以提高扫读效率；紧凑的 padding、较短行高与紧字距适配高频比较和快速决策。主色选择低存在感的 slate，保证商品图片、价格和库存状态成为第一视觉焦点；accent 使用 orange 强化‘到手价/立即拼团/限时抢购’等转化动作。阴影仅用轻量 shadow-sm，避免电商感过重导致界面松散；边框采用浅灰细线，适合 2-4 列响应式商品网格，清晰区分卡片但不过度分割。整体保持无玻璃拟态、无 serif 倾向、无冗余装饰，符合小程序轻量、快速、信任驱动的选品与履约闭环。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-emerald-600 text-white shadow-sm hover:bg-emerald-700","functional_audit_result":"CORRECTION_NEEDED: \n1. flow_1 / flow_2 / flow_3 / flow_4 all reference navigation into pages that are not actually traversable via matching hash links from the intended source pages:\n   - The sidebar links go to #pg1–#pg13, but the task flows require transitions like “进入选品中心 -&gt; 使用多维筛选条件 -&gt; 打开商品详情 -&gt; 加入选品清单 -&gt; 一键上架到团购池”.\n   - In several places the prototype uses placeholder hashes such as #drawer-open, #list-add, #group-buy-pool, #analytics-risk that do not correspond to real routed pages/sections with those IDs.\n\n2. flow_1 broken path:\n   - “打开商品详情” from 选品中心 exists only as click-to-open drawer behavior, but there is no hash link from 选品中心 to 商品详情 page/section as required by the audit rule.\n   - “加入选品清单” and “一键上架到团购池” appear as anchors, but many point to placeholder hashes or same-page placeholders rather than a concrete traversable route.\n   - The intended completion flow is not explicitly connected end-to-end with a stable hash path.\n\n3. flow_2 broken path:\n   - “查看智能推荐理由” is present on pg4, but the route to a distinct page/section for recommendation details is incomplete/inconsistent.\n   - “标记通过” / “淘汰” buttons exist in drawers, but they point to #drawer-open or same current hash instead of a dedicated actionable destination, so the evaluation flow is not logically traversable per hash-link rule.\n\n4. flow_3 broken path:\n   - “进入数据看板” exists, but “查看补货预警与滞销列表” and “打开商品详情” are not connected through a clear hash-based page sequence.\n   - “调整活动或补货建议” is shown as information, but there is no actionable button/link to a dedicated adjustment page or anchored workflow.\n   - “更新选品清单” exists, but again is not part of a fully linked end-to-end route.\n\n5. flow_4 broken path:\n   - “进入数据看板 -&gt; 选择品类或时间范围 -&gt; 查看供应商中心与商品表现 -&gt; 标记高风险供应商 -&gt; 优化后续选品策略” is only partially represented.\n   - There is no distinct, hash-addressable control for “标记高风险供应商”; current UI only displays supplier risk cards and generic strategy text.\n   - The “优化后续选品策略” action is informational, not a traversable action button tied to a destination.\n\n6. Data consistency issues:\n   - Several links reference pages/targets not defined by IDs in the DOM, causing the prototype to fail the hash-based traversal requirement.\n   - Some actions are duplicated as non-functional buttons in the global drawer and page content without a clear submit/complete step.\n\n","visual_accentColor":"orange","visual_shadowStrategy":"shadow-sm","visual_borderAccent":"border-slate-100","visual_glassIntensity":"none","visual_lineHeight":"leading-snug","visual_letterSpacing":"tracking-tight","visual_serifBias":"false","shell_pattern":"SIDEBAR_PRIMARY_NAV","content_mode":"SIDEBAR_FIRST","shape_primary_goal":"TRANSACT","shape_content_unit":"LISTING","shape_consumption_mode":"DISCOVER_FIRST","shape_media_weight":"MIXED","shape_layout_rhythm":"COMPACT_CARD","shape_content_density":"MEDIUM","shape_navigation_mode":"CATEGORY","shape_main_loop":"COMPARE_BUY","shape_ui_tone":"EDITORIAL","shape_signal_priority":"[PRICE, HEAT]","design_ready":"false","data_ready":"true","visual_ready":"true"}</t>
         </is>
       </c>
     </row>
@@ -293,7 +174,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>深夜食堂预约场景的核心不是高效率的信息密度，而是“即时安抚 + 低门槛预订 + 夜间氛围感”。因此整体采用深色夜间底色来建立深夜语境与安静感，用琥珀色作为少量高对比强调，承载‘可订位’、‘确认’、‘营业中’等关键动作提示，帮助用户在夜间快速决策。卡片采用中等密度的容器样式，兼顾表单填写的清晰性与门店信息、环境图、可订时段等辅助模块的分区感，符合固定顶部导航 + 动态侧栏的布局策略。字体选择无衬线以提高表单与状态信息的可读性，行高和字距偏紧以适配预约任务流的短路径浏览，整体传达稳、暖、可信、可立即完成预约的体验。</t>
+          <t>深夜食堂预约的视觉核心是“温暖陪伴 + 即时信任 + 低门槛下单”。因此整体采用夜间深色底，既符合深夜场景，也能让营业状态、可预约时段和关键CTA更突出；卡片使用轻微玻璃质感与细边框，建立安静、可信、不过度打扰的氛围。作为预约型产品，页面需要高信息密度但不能显得拥挤，所以采用紧凑内边距、轻量阴影和明确分区，适配营业状态、菜单、人数/时段表单、备注与确认模块的并列展示。字体选择无衬线以提升移动端可读性与操作效率，行高偏紧以增强发现密度，字距保持紧凑，帮助用户在疲惫状态下快速扫读可订信息。主色用琥珀色传达夜宵、热食与温度感，辅以偏清新的绿色作为可用/成功反馈，强化“能订、可订、放心订”的信号。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -309,7 +190,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-slate-950","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"用户从首页快速发现可订位时段，并提交预约完成确认闭环。\",\"steps\":[\"ENTRY：首页推荐预约时段卡\",\"ACTION：选择日期、时间、人数并提交手机号\",\"FEEDBACK：展示预约成功页、预约编号与短信通知说明\"]},{\"id\":\"flow_2\",\"description\":\"用户先查看门店详情与氛围，再进入预约表单完成订位。\",\"steps\":[\"ENTRY：门店详情页的实时余位提示\",\"ACTION：查看交通、营业时间后点击预约按钮并填写表单\",\"FEEDBACK：表单提交后跳转预约确认页并展示到店提醒入口\"]},{\"id\":\"flow_3\",\"description\":\"用户在个人中心管理已有预约，完成改期或取消后获得状态更新。\",\"steps\":[\"ENTRY：我的预约页的当前订单卡片\",\"ACTION：点击改期或取消并确认操作\",\"FEEDBACK：页面状态更新、通知中心出现变更消息\"]}]","visual_primaryColor":"slate","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-slate-800 bg-slate-900/90 p-5 md:p-6","visual_reasoning":"深夜食堂预约场景的核心不是高效率的信息密度，而是“即时安抚 + 低门槛预订 + 夜间氛围感”。因此整体采用深色夜间底色来建立深夜语境与安静感，用琥珀色作为少量高对比强调，承载‘可订位’、‘确认’、‘营业中’等关键动作提示，帮助用户在夜间快速决策。卡片采用中等密度的容器样式，兼顾表单填写的清晰性与门店信息、环境图、可订时段等辅助模块的分区感，符合固定顶部导航 + 动态侧栏的布局策略。字体选择无衬线以提高表单与状态信息的可读性，行高和字距偏紧以适配预约任务流的短路径浏览，整体传达稳、暖、可信、可立即完成预约的体验。","lang":"ZH","visual_buttonClass":"rounded-xl bg-amber-500 text-stone-950 font-semibold shadow-lg hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n- flow_1: “预约首页 -&gt; 在线预约页”有入口，但“在线预约页 -&gt; 填写人数与时间 -&gt; 订单确认页 -&gt; 支付定金 -&gt; 预约成功页”不够完整可遍历。`#pg1-booking` 里只有“去订单确认页 / 支付定金后成功页”，缺少明确的“填写人数与时间”提交动作；且“支付定金”没有明确从订单确认页继续到成功页的可操作提交按钮链路。  \n- flow_2: “预约成功页 -&gt; 点击改签 -&gt; 在线预约页”在 `#pg1-success` 有“点击改签”，但后续“在线预约页 -&gt; 重新选择时间 -&gt; 订单确认页 -&gt; 更新成功提示”缺少明确的“重新选择时间”提交/确认动作与“更新成功提示”页面/按钮链路，且成功提示文案与页面跳转不一致。  \n- flow_3: “管理看板 -&gt; 预约管理页”存在入口，但“筛选高峰时段订单 -&gt; 分配桌位 -&gt; 标记确认 -&gt; 更新实时状态”中，`#pg6` 的“分配桌位”“标记确认并同步状态”是按钮样式但没有对应 hash 跳转或可验证的完成页/状态页；另外 `#pg5`/`#pg6` 对“管理看板”与“预约管理页”的命名和跳转关系混乱，无法确认从看板到管理页的单一路径。  \n- flow_4: “管理看板 -&gt; 查看风险列表 -&gt; 打开顾客详情 -&gt; 发送提醒消息 -&gt; 调整桌位预留 -&gt; 结果记录”不完整。虽然有“风险列表”入口和弹窗详情，但“发送提醒消息”“调整桌位预留”“结果记录”缺少明确的可遍历提交/确认路径或结果页面；部分按钮只是静态按钮，没有链接到目标步骤。  \n- 页面/锚点命名混乱：`#pg5` 标题为“预约管理”，但页面内又出现“返回管理看板 / 去在线预约页 / 订单确认页”等与 flow 定义不一致的导航；`#pg6` 标题为“数据看板”，却承载大量预约管理内容，导致任务流中的“管理看板 / 预约管理页 / 查看风险列表”等页面对应不清晰。  \n- 缺失明确“更新成功提示 / 结果记录”页面：任务流要求的最终反馈页在 prototype 中没有独立、明确、可跳转验证的目标。","visual_accentColor":"amber","visual_shadowStrategy":"shadow-xl","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-snug","visual_letterSpacing":"tracking-tight","visual_serifBias":"false"}</t>
+          <t>{"visual_bgClass":"bg-gradient-to-b from-stone-950 via-zinc-950 to-neutral-950","taskFlows":"[{\"id\":\"flow_01\",\"description\":\"用户从首页快速确认可订并完成预约。\",\"steps\":[\"入口：首页推荐时段卡 -&gt; 动作：选择推荐时段并进入预约表单 -&gt; 反馈：表单预填并展示可订成功提示\"]},{\"id\":\"flow_02\",\"description\":\"用户在预约表单中提交订位信息并获得确认。\",\"steps\":[\"入口：预约表单页 -&gt; 动作：选择日期、时段、人数并填写手机号后提交 -&gt; 反馈：弹出预约成功确认页，显示预约编号和短信通知说明\"]},{\"id\":\"flow_03\",\"description\":\"用户在确认页或个人中心进行改期与取消操作。\",\"steps\":[\"入口：预约确认页/我的预约页 -&gt; 动作：点击改期或取消并完成确认 -&gt; 反馈：状态实时更新，通知中心同步生成改期或取消确认消息\"]},{\"id\":\"flow_comment_reply\",\"description\":\"Users can enter a detail view, comment, reply, and see the thread update immediately.\",\"steps\":[\"ENTRY: Open the detail view from a discovery or content card\",\"ACTION: Add a comment or reply to an existing thread\",\"FEEDBACK: Comment thread updates instantly and interaction counts increase\"]},{\"id\":\"flow_return_to_feed\",\"description\":\"Users return from detail view back into the discovery/feed context without losing browsing continuity.\",\"steps\":[\"ENTRY: Open a detail view from the main discovery feed\",\"ACTION: Close the detail overlay or navigate back\",\"FEEDBACK: The user returns to the original feed context and can continue browsing\"]}]","visual_primaryColor":"amber-400","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-white/10 bg-white/6 p-4 md:p-5 text-stone-100","visual_reasoning":"深夜食堂预约的视觉核心是“温暖陪伴 + 即时信任 + 低门槛下单”。因此整体采用夜间深色底，既符合深夜场景，也能让营业状态、可预约时段和关键CTA更突出；卡片使用轻微玻璃质感与细边框，建立安静、可信、不过度打扰的氛围。作为预约型产品，页面需要高信息密度但不能显得拥挤，所以采用紧凑内边距、轻量阴影和明确分区，适配营业状态、菜单、人数/时段表单、备注与确认模块的并列展示。字体选择无衬线以提升移动端可读性与操作效率，行高偏紧以增强发现密度，字距保持紧凑，帮助用户在疲惫状态下快速扫读可订信息。主色用琥珀色传达夜宵、热食与温度感，辅以偏清新的绿色作为可用/成功反馈，强化“能订、可订、放心订”的信号。","lang":"ZH","visual_buttonClass":"rounded-xl bg-amber-500 text-stone-950 font-semibold shadow-lg hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n- flow_1: “预约首页 -&gt; 在线预约页”有入口，但“在线预约页 -&gt; 填写人数与时间 -&gt; 订单确认页 -&gt; 支付定金 -&gt; 预约成功页”不够完整可遍历。`#pg1-booking` 里只有“去订单确认页 / 支付定金后成功页”，缺少明确的“填写人数与时间”提交动作；且“支付定金”没有明确从订单确认页继续到成功页的可操作提交按钮链路。  \n- flow_2: “预约成功页 -&gt; 点击改签 -&gt; 在线预约页”在 `#pg1-success` 有“点击改签”，但后续“在线预约页 -&gt; 重新选择时间 -&gt; 订单确认页 -&gt; 更新成功提示”缺少明确的“重新选择时间”提交/确认动作与“更新成功提示”页面/按钮链路，且成功提示文案与页面跳转不一致。  \n- flow_3: “管理看板 -&gt; 预约管理页”存在入口，但“筛选高峰时段订单 -&gt; 分配桌位 -&gt; 标记确认 -&gt; 更新实时状态”中，`#pg6` 的“分配桌位”“标记确认并同步状态”是按钮样式但没有对应 hash 跳转或可验证的完成页/状态页；另外 `#pg5`/`#pg6` 对“管理看板”与“预约管理页”的命名和跳转关系混乱，无法确认从看板到管理页的单一路径。  \n- flow_4: “管理看板 -&gt; 查看风险列表 -&gt; 打开顾客详情 -&gt; 发送提醒消息 -&gt; 调整桌位预留 -&gt; 结果记录”不完整。虽然有“风险列表”入口和弹窗详情，但“发送提醒消息”“调整桌位预留”“结果记录”缺少明确的可遍历提交/确认路径或结果页面；部分按钮只是静态按钮，没有链接到目标步骤。  \n- 页面/锚点命名混乱：`#pg5` 标题为“预约管理”，但页面内又出现“返回管理看板 / 去在线预约页 / 订单确认页”等与 flow 定义不一致的导航；`#pg6` 标题为“数据看板”，却承载大量预约管理内容，导致任务流中的“管理看板 / 预约管理页 / 查看风险列表”等页面对应不清晰。  \n- 缺失明确“更新成功提示 / 结果记录”页面：任务流要求的最终反馈页在 prototype 中没有独立、明确、可跳转验证的目标。","visual_accentColor":"emerald-300","visual_shadowStrategy":"shadow-sm","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-snug","visual_letterSpacing":"tracking-tight","visual_serifBias":"false","shell_pattern":"SIDEBAR_PRIMARY_NAV","content_mode":"SIDEBAR_FIRST","shape_primary_goal":"TRANSACT","shape_content_unit":"LISTING","shape_consumption_mode":"DISCOVER_FIRST","shape_media_weight":"MIXED","shape_layout_rhythm":"COMPACT_CARD","shape_content_density":"MEDIUM","shape_navigation_mode":"CATEGORY","shape_main_loop":"COMPARE_BUY","shape_ui_tone":"EDITORIAL","shape_signal_priority":"[PRICE, HEAT]","design_ready":"false","data_ready":"true","visual_ready":"true"}</t>
         </is>
       </c>
     </row>
@@ -321,7 +202,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>该平台的核心是“感官探索 + 社群共识 + 口味可视化反馈”，因此视觉上应建立可信、专业但不冰冷的啤酒评鉴氛围。背景采用温润的 stone 系列，能承接酒液、麦芽与发酵质感；卡片使用白底微透与细边框，适合 12 栅格下的多模块并列信息，兼顾酒款详情、评分维度、评论流与推荐位的可读性。整体信息密度保持中等，使用 relaxed 行高与 normal 字距，确保专业参数、风味标签与社群内容都能被快速扫读。主色选择 amber，呼应麦芽与啤酒液体色泽，适合作为评分、关键数值和状态提示；辅色 emerald 用于“收藏 / 想喝 / 已喝”与推荐关联，强化探索与正反馈。阴影仅用轻量 shadow-sm，避免社交内容与专业数据区域之间产生过度层级干扰；同时启用轻度玻璃感以增强层次，但不削弱信息清晰度。字体维持 sans，可更好承载多维评分、风味轮与列表密度，符合 persistent top + dynamic sidebar 的结构需求。</t>
+          <t>This product needs a high-density Visual DNA that supports the full loop of discovery, scoring, comparison, and social validation. A deep slate base creates a serious, catalog-like atmosphere that fits professional beer evaluation and keeps the interface focused on data. Tight, compact card styling and subtle borders support the persistent-top / dynamic-sidebar shell by maximizing information density across beer details, rating dimensions, flavor tags, drink logs, and community commentary. An amber accent evokes craft beer warmth, flavor, and tasting notes without overpowering the analytical structure. Sans-serif typography with tight tracking and snug leading improves scanability for dense hierarchies such as ABV, IBU, style, scores, and peer comparisons. Light blur adds a modern, premium layer for side panels and filters while preserving legibility. Overall, the visual system balances sensory exploration with community consensus: it feels exploratory and social, but still precise enough for serious tasting and comparison workflows.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -337,12 +218,11 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{"visual_bgClass":"bg-stone-50","taskFlows":"[{\"id\":\"flow_1\",\"description\":\"从首页发现酒款并完成首次评分反馈闭环。\",\"steps\":[\"ENTRY：首页热门酒款卡片点击\",\"ACTION：进入酒款详情页，查看风味标签、评分分布并提交多维评分与短评\",\"FEEDBACK：评分立即刷新为个人已评分状态，社区均值与趋势图更新，并出现提交成功提示\"]},{\"id\":\"flow_2\",\"description\":\"从搜索进入目标酒款后记录喝后感并沉淀到个人口味档案。\",\"steps\":[\"ENTRY：顶部搜索框搜索酒款名称或风味标签\",\"ACTION：打开目标酒款详情，添加评论、上传图片、标记喝过状态\",\"FEEDBACK：评论出现在详情页与个人主页评分历史中，喝过统计同步增加\"]},{\"id\":\"flow_3\",\"description\":\"通过社区共识发现相似酒款并持续探索。\",\"steps\":[\"ENTRY：社区推荐页点击高分短评或热门讨论酒款\",\"ACTION：查看详情后点击相似推荐列表中的其他酒款继续浏览\",\"FEEDBACK：推荐列表根据浏览与评分实时调整，形成连续探索路径与偏好强化\"]}]","visual_primaryColor":"amber-600","visual_fontFamily":"font-sans","visual_cardClass":"rounded-2xl border border-slate-100 bg-white/90 p-5 md:p-6","visual_reasoning":"该平台的核心是“感官探索 + 社群共识 + 口味可视化反馈”，因此视觉上应建立可信、专业但不冰冷的啤酒评鉴氛围。背景采用温润的 stone 系列，能承接酒液、麦芽与发酵质感；卡片使用白底微透与细边框，适合 12 栅格下的多模块并列信息，兼顾酒款详情、评分维度、评论流与推荐位的可读性。整体信息密度保持中等，使用 relaxed 行高与 normal 字距，确保专业参数、风味标签与社群内容都能被快速扫读。主色选择 amber，呼应麦芽与啤酒液体色泽，适合作为评分、关键数值和状态提示；辅色 emerald 用于“收藏 / 想喝 / 已喝”与推荐关联，强化探索与正反馈。阴影仅用轻量 shadow-sm，避免社交内容与专业数据区域之间产生过度层级干扰；同时启用轻度玻璃感以增强层次，但不削弱信息清晰度。字体维持 sans，可更好承载多维评分、风味轮与列表密度，符合 persistent top + dynamic sidebar 的结构需求。","lang":"ZH","visual_buttonClass":"rounded-2xl bg-amber-500 text-stone-950 font-semibold hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n1. `/dashboard -&gt; /tastings` is not actually implemented as a reachable page/route. The prototype only contains hash targets like `#pg2`, `#pg3`, etc., and there is no dedicated `#tastings` section or page. Multiple buttons point to `#tastings`, but no matching destination exists.  \n2. `/dashboard -&gt; /profile` is broken for the same reason: buttons point to `#profile`, but there is no `#profile` page/section in the prototype.  \n3. `/dashboard -&gt; /recommendations` is broken: buttons point to `#recommendations`, but there is no `#recommendations` page/section in the prototype.  \n4. `/dashboard -&gt; /insights` is broken: buttons point to `#insights`, but there is no `#insights` page/section in the prototype.  \n5. Flow 1 is missing the core “填写品鉴信息与多维评分” form interaction and the “保存记录” action. The prototype shows record cards and a detail drawer, but no input form, no submit/save button, and no explicit result-update action after saving.  \n6. Flow 2 is missing the “阅读偏好雷达图与风格阈值” and “查看推荐解释” in a dedicated `/profile` page; those elements exist under `#pg4`, but the requested route hash is absent and therefore not logically traversable as specified.  \n7. Flow 3 is missing the required “按匹配度筛选” interaction in a functional sense. The recommendations page contains explanatory text mentioning matching, but there is no actual filter control/UI to perform the筛选. It also lacks a clear “收藏目标啤酒” action button tied to the recommendation items; the page shows collection status labels, not a save/favorite action.  \n8. Flow 4 is missing the required “选择时间区间” control and the explicit “生成复盘结论” action. The insights content is static; there is no time-range selector or generation/submit control.","visual_accentColor":"emerald-500","visual_shadowStrategy":"shadow-sm","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-relaxed","visual_letterSpacing":"tracking-normal","visual_serifBias":"false"}</t>
+          <t>{"visual_bgClass":"bg-slate-950","taskFlows":"[{\"id\":\"TF-01\",\"description\":\"发现一款酒并完成首次判断\",\"steps\":[\"ENTRY：首页热门酒款卡片点击 -&gt; ACTION：进入酒款详情查看风味参数、评分分布与社区短评 -&gt; FEEDBACK：详情页高亮个人可操作区，并出现“加入想喝/收藏/去评分”状态反馈\"]},{\"id\":\"TF-02\",\"description\":\"完成多维评分与喝后感记录闭环\",\"steps\":[\"ENTRY：酒款详情页点击“去评分” -&gt; ACTION：在评论编辑页填写香气、苦度、酒体、回味、平衡度与喝后感并提交 -&gt; FEEDBACK：返回详情页后评分均值更新、个人记录写入时间线并显示提交成功提示\"]},{\"id\":\"TF-03\",\"description\":\"基于风味标签继续探索相似酒款\",\"steps\":[\"ENTRY：风味探索页点击某个风味标签或风味轮区域 -&gt; ACTION：查看相似酒款推荐并切换筛选条件 -&gt; FEEDBACK：结果列表即时重排，出现‘已应用筛选’回显与相似度提示\"]},{\"id\":\"TF-04\",\"description\":\"通过社区共识验证一款争议酒的口碑\",\"steps\":[\"ENTRY：社区推荐页点击争议酒款卡片 -&gt; ACTION：浏览评分分布、近期趋势与不同资历层评论 -&gt; FEEDBACK：页面展示共识摘要、分歧点标签与可继续进入详情的清晰路径\"]},{\"id\":\"TF-05\",\"description\":\"管理个人口味档案并校准推荐\",\"steps\":[\"ENTRY：个人主页进入口味档案模块 -&gt; ACTION：查看常见偏好、回避风味与历史评分并调整状态标记 -&gt; FEEDBACK：个人画像实时更新，推荐内容随之刷新并提示档案已保存\"]}]","visual_primaryColor":"slate","visual_fontFamily":"font-sans","visual_cardClass":"rounded-xl border border-slate-800 bg-slate-900/80 p-4 md:p-5","visual_reasoning":"This product needs a high-density Visual DNA that supports the full loop of discovery, scoring, comparison, and social validation. A deep slate base creates a serious, catalog-like atmosphere that fits professional beer evaluation and keeps the interface focused on data. Tight, compact card styling and subtle borders support the persistent-top / dynamic-sidebar shell by maximizing information density across beer details, rating dimensions, flavor tags, drink logs, and community commentary. An amber accent evokes craft beer warmth, flavor, and tasting notes without overpowering the analytical structure. Sans-serif typography with tight tracking and snug leading improves scanability for dense hierarchies such as ABV, IBU, style, scores, and peer comparisons. Light blur adds a modern, premium layer for side panels and filters while preserving legibility. Overall, the visual system balances sensory exploration with community consensus: it feels exploratory and social, but still precise enough for serious tasting and comparison workflows.","lang":"ZH","visual_buttonClass":"rounded-2xl bg-amber-500 text-stone-950 font-semibold hover:bg-amber-400","functional_audit_result":"CORRECTION_NEEDED:  \n1. `/dashboard -&gt; /tastings` is not actually implemented as a reachable page/route. The prototype only contains hash targets like `#pg2`, `#pg3`, etc., and there is no dedicated `#tastings` section or page. Multiple buttons point to `#tastings`, but no matching destination exists.  \n2. `/dashboard -&gt; /profile` is broken for the same reason: buttons point to `#profile`, but there is no `#profile` page/section in the prototype.  \n3. `/dashboard -&gt; /recommendations` is broken: buttons point to `#recommendations`, but there is no `#recommendations` page/section in the prototype.  \n4. `/dashboard -&gt; /insights` is broken: buttons point to `#insights`, but there is no `#insights` page/section in the prototype.  \n5. Flow 1 is missing the core “填写品鉴信息与多维评分” form interaction and the “保存记录” action. The prototype shows record cards and a detail drawer, but no input form, no submit/save button, and no explicit result-update action after saving.  \n6. Flow 2 is missing the “阅读偏好雷达图与风格阈值” and “查看推荐解释” in a dedicated `/profile` page; those elements exist under `#pg4`, but the requested route hash is absent and therefore not logically traversable as specified.  \n7. Flow 3 is missing the required “按匹配度筛选” interaction in a functional sense. The recommendations page contains explanatory text mentioning matching, but there is no actual filter control/UI to perform the筛选. It also lacks a clear “收藏目标啤酒” action button tied to the recommendation items; the page shows collection status labels, not a save/favorite action.  \n8. Flow 4 is missing the required “选择时间区间” control and the explicit “生成复盘结论” action. The insights content is static; there is no time-range selector or generation/submit control.","visual_accentColor":"amber","visual_shadowStrategy":"shadow-sm","visual_borderAccent":"border-slate-100","visual_glassIntensity":"backdrop-blur-md","visual_lineHeight":"leading-snug","visual_letterSpacing":"tracking-tight","visual_serifBias":"false","shell_pattern":"PERSISTENT_TOP_DYNAMIC_SIDEBAR","content_mode":"CONTENT_FIRST","shape_primary_goal":"DISCOVER","shape_content_unit":"POST","shape_consumption_mode":"DISCOVER_FIRST","shape_media_weight":"VISUAL_HEAVY","shape_layout_rhythm":"WATERFALL","shape_content_density":"MEDIUM","shape_navigation_mode":"TOPIC_TAB","shape_main_loop":"SCROLL_DISCOVER","shape_ui_tone":"LIVELY","shape_signal_priority":"[SAVE_RATE, HEAT]","design_ready":"false","data_ready":"true","visual_ready":"true"}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>